--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -742,14 +742,14 @@
       <c r="E4" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>22.1</v>
+      <c r="F4" s="8" t="n">
+        <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12.5</v>
+        <v>23.5</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.8</v>
@@ -758,37 +758,43 @@
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>26.6</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n">
+        <v>43.1</v>
+      </c>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="T4" s="3" t="n"/>
+      <c r="T4" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>20.3</v>
+        <v>80.3</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>26.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>3.3</v>
@@ -814,48 +820,51 @@
         <v>16.9</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>22.5</v>
+        <v>26.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+        <v>1.3</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>438</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>18.3</v>
-      </c>
+          <t xml:space="preserve">99
+211
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v>41.6</v>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.3</v>
+        <v>21.3</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>74.3</v>
+        <v>94.3</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>8</v>
@@ -893,13 +902,13 @@
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>11.9</v>
+      <c r="G6" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>15.2</v>
@@ -908,25 +917,28 @@
         <v>3.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>72.5</v>
+        <v>5.2</v>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16495171
+178
+2 2 4221
+</t>
+        </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>17.9</v>
+        <v>16.8</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P6" s="8" t="n">
-        <v>41.6</v>
+        <v>25.1</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>26.8</v>
@@ -935,25 +947,25 @@
         <v>22.3</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>21.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>2.1</v>
@@ -972,22 +984,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>274.4</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>34.4</v>
+      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>22.8</v>
+        <v>18.8</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>3</v>
@@ -996,28 +1006,28 @@
         <v>4.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>17.9</v>
+      <c r="M7" s="8" t="n">
+        <v>72.90000000000001</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>882.1</v>
+        <v>94</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>21.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>22.7</v>
+      <c r="R7" s="8" t="n">
+        <v>28.7</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>24.9</v>
@@ -1035,13 +1045,13 @@
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>22.1</v>
+        <v>18.1</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>90</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1057,16 +1067,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>260.2</v>
+        <v>1602.4</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>28.4</v>
+        <v>2.4</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22.7</v>
+        <v>2.2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>11.4</v>
@@ -1078,28 +1088,24 @@
         <v>2.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>16.6</v>
-      </c>
+        <v>13.3</v>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>458</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>1862.8</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n">
-        <v>882.1</v>
+        <v>89.8</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>46.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>445.1</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>22.8</v>
@@ -1108,10 +1114,10 @@
         <v>26.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>19.6</v>
@@ -1122,8 +1128,12 @@
       <c r="X8" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Y8" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1138,22 +1148,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>77.8</v>
-      </c>
+        <v>1602.4</v>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.7</v>
+        <v>62.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.8</v>
@@ -1162,51 +1166,49 @@
         <v>28.8</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>37.1</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>814.5</v>
+        <v>15.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>98.2</v>
+        <v>7.5</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>23.1</v>
+        <v>88.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>3.7</v>
+        <v>127.1</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>184.2</v>
+        <v>389.2</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>38.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>12.7</v>
+      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1221,75 +1223,85 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>13.5</v>
-      </c>
+        <v>146.4</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4465227
+8179171
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2282891
+181
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82828
+199812
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792871272
+1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>17</v>
+        <v>84.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>98</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+2
+</t>
+        </is>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>25.1</v>
+        <v>2.5</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7424
+1111
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n">
-        <v>18.5</v>
+        <v>7.7</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>45.1</v>
+      </c>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1304,76 +1316,68 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>29.5</v>
-      </c>
+        <v>498.5</v>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>16.9</v>
+        <v>4.6</v>
+      </c>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77718
+6222
+</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>22.2</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+24721195
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>76.8</v>
+        <v>6.8</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>6.6</v>
+      <c r="V11" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>89</v>
+        <v>896</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1389,7 +1393,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>299.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>26.5</v>
@@ -1401,43 +1405,39 @@
         <v>31.3</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>97.7</v>
+      </c>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>31.9</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>17</v>
+        <v>17.8</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>98</v>
+        <v>166.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>39</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>68.40000000000001</v>
@@ -1446,19 +1446,19 @@
         <v>10.6</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>84.5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1488,27 +1488,31 @@
       <c r="G13" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>15</v>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+1109
+</t>
+        </is>
       </c>
       <c r="I13" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>39.4</v>
+      <c r="J13" s="3" t="n">
+        <v>3.4</v>
       </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>17.6</v>
+        <v>17</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1.6</v>
@@ -1520,22 +1524,22 @@
         <v>19.5</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>22.2</v>
+        <v>2.5</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>93</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.6</v>
+        <v>1.6</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>89.09999999999999</v>
@@ -1557,58 +1561,50 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>223.8</v>
+        <v>323.8</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>728.5</v>
+        <v>27.5</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>922.5</v>
-      </c>
+      <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>14.8</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>18.4</v>
+        <v>2.6</v>
+      </c>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="8" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>22.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>11.4</v>
+      <c r="R14" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>427.1</v>
+        <v>23.7</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>6.8</v>
@@ -1620,11 +1616,9 @@
         <v>19.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>95.8</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="n">
         <v>0.9</v>
       </c>
@@ -1642,7 +1636,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>260</v>
+        <v>266.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>24.8</v>
@@ -1650,49 +1644,41 @@
       <c r="E15" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="8" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>32.4</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K15" s="3" t="n"/>
+        <v>22.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="L15" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>89.59999999999999</v>
-      </c>
+        <v>6.1</v>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>21</v>
+        <v>2.6</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>41</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>19.7</v>
@@ -1701,10 +1687,10 @@
         <v>19.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0.7</v>
@@ -1723,7 +1709,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8934.799999999999</v>
+        <v>34.8</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>28.3</v>
@@ -1732,10 +1718,10 @@
         <v>16.6</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2922.5</v>
+        <v>2.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>14.4</v>
@@ -1746,38 +1732,38 @@
       <c r="J16" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K16" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>16.6</v>
+        <v>82.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>94</v>
+        <v>2.6</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>22.1</v>
+        <v>158.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>229.1</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>1.1</v>
+        <v>41.4</v>
+      </c>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21214
+7922
+</t>
+        </is>
       </c>
       <c r="U16" s="3" t="n">
-        <v>15</v>
+        <v>15.7</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>19.2</v>
@@ -1786,13 +1772,13 @@
         <v>18.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>80.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>91</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1807,74 +1793,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>15646.8</v>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n">
-        <v>137.2</v>
+        <v>3.3</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>9.9</v>
-      </c>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K17" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L17" s="3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="M17" s="3" t="n">
-        <v>85.3</v>
+        <v>16.6</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>86559.39999999999</v>
-      </c>
+        <v>9.5</v>
+      </c>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="R17" s="3" t="n">
-        <v>21.8</v>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">744
+981
+</t>
+        </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>59.1</v>
+        <v>755.6</v>
+      </c>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n">
+        <v>3.5</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>9.699999999999999</v>
+      <c r="W17" s="8" t="n">
+        <v>612.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>20.3</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>10.4</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
@@ -1893,74 +1875,67 @@
       <c r="C18" s="3" t="n">
         <v>312.4</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="D18" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>91.7</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="3" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>44.6</v>
+        <v>0.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 99
-</t>
-        </is>
+        <v>534.1</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>93.2</v>
+        <v>23.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S18" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>188.1</v>
+        <v>185.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>7</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>57.4</v>
+        <v>2</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>21.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>2.1</v>
@@ -1978,44 +1953,42 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>1253.4</v>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0.1</v>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77718
+273
+</t>
+        </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>16.4</v>
-      </c>
+        <v>7.7</v>
+      </c>
+      <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n">
-        <v>3</v>
+        <v>30.3</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>14.1</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.7</v>
@@ -2027,29 +2000,27 @@
         <v>21.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>29.3</v>
+        <v>23.5</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>66.5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>21.9</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="Z19" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2063,24 +2034,22 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n">
-        <v>12.2</v>
+      <c r="I20" s="8" t="n">
+        <v>45482.4</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.3</v>
@@ -2092,43 +2061,41 @@
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="R20" s="8" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>23.4</v>
+        <v>3.1</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>34.1</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>19.9</v>
+        <v>18.9</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>20.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>14.1</v>
+        <v>83.5</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>7.6</v>
@@ -2147,46 +2114,47 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1253.4</v>
+        <v>253.4</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>21.8</v>
+        <v>88.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>11.9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828127
+160
+745414119
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>17.9</v>
+        <v>1.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>2.3</v>
+        <v>28.3</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>22.8</v>
@@ -2194,26 +2162,30 @@
       <c r="R21" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S21" s="8" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>14</v>
+      <c r="S21" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+1 1
+</t>
+        </is>
       </c>
       <c r="U21" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>20.2</v>
+      <c r="W21" s="8" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.2</v>
+        <v>12.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>1.5</v>
@@ -2232,46 +2204,50 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>5334.9</v>
+        <v>266.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>12.6</v>
+        <v>13</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="8" t="n">
+        <v>428.2</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
+        <v>3.2</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+77
+</t>
+        </is>
       </c>
       <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P22" s="3" t="n">
-        <v>12.2</v>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+2
+</t>
+        </is>
       </c>
       <c r="Q22" s="3" t="n">
         <v>20.9</v>
@@ -2279,23 +2255,27 @@
       <c r="R22" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>11.2</v>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="X22" s="8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">449
+190
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+1856
+</t>
+        </is>
       </c>
       <c r="Y22" s="3" t="n">
         <v>96.8</v>
@@ -2317,7 +2297,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1548.6</v>
+        <v>39.2</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>27.6</v>
@@ -2326,49 +2306,45 @@
         <v>17</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>310.6</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
+        <v>6.6</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>0.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>616.3</v>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>117.1</v>
+        <v>17.4</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>10.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>25.1</v>
+        <v>251.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.5</v>
+        <v>21.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0.5</v>
+        <v>23.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>393.1</v>
+        <v>40</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2376,8 +2352,12 @@
       <c r="V23" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="W23" s="3" t="n">
-        <v>99.8</v>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">449
+190
+</t>
+        </is>
       </c>
       <c r="X23" s="3" t="n">
         <v>19.6</v>
@@ -2402,77 +2382,69 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>30.9</v>
+        <v>58.6</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>737.6</v>
+        <v>3.7</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>115.9</v>
+        <v>851</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>57.6</v>
+        <v>57.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>14.8</v>
+        <v>6.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>19.3</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>869.2</v>
+        <v>49.1</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>6.3</v>
+        <v>63.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>14.3</v>
+        <v>1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>38.1</v>
+        <v>10.7</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>75.2</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>78.7</v>
+        <v>93.7</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>19.9</v>
-      </c>
+        <v>37.1</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="3" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>6.3</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="Y24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2487,43 +2459,43 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>279.8</v>
+        <v>39.7</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>70.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>29.8</v>
+        <v>144.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>24.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>18.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>87.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>938</v>
+        <v>38.1</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>1.3</v>
@@ -2532,31 +2504,29 @@
         <v>39.1</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>82.5</v>
+        <v>6.4</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>20.1</v>
+        <v>2.8</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>18</v>
+        <v>0.2</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>75</v>
-      </c>
+        <v>21.1</v>
+      </c>
+      <c r="Y25" s="3" t="n"/>
       <c r="Z25" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2572,73 +2542,63 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>341.4</v>
+        <v>279.8</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>17.4</v>
-      </c>
+        <v>94.8</v>
+      </c>
+      <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n">
-        <v>21.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>12</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>18.2</v>
+        <v>17.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>14.6</v>
+        <v>20</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>9.9</v>
-      </c>
+        <v>86.5</v>
+      </c>
+      <c r="U26" s="3" t="n"/>
       <c r="V26" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>19.7</v>
+        <v>21.1</v>
+      </c>
+      <c r="W26" s="8" t="n">
+        <v>802</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>6.3</v>
@@ -2657,73 +2617,81 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>343.6</v>
+        <v>341.4</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>15.8</v>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792
+67
+</t>
+        </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>20.3</v>
+        <v>0.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>149.9</v>
+        <v>9</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+1119
+</t>
+        </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>18.5</v>
+        <v>25.2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.9</v>
+        <v>2.6</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.7</v>
+        <v>1.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>11.8</v>
+        <v>2.5</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>22.7</v>
+        <v>41.1</v>
       </c>
       <c r="R27" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="S27" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>82.40000000000001</v>
-      </c>
       <c r="Y27" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.9</v>
@@ -2742,76 +2710,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5.1</v>
+        <v>370</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>81.7</v>
-      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792
+67
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>70.7</v>
-      </c>
+      <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>4.6</v>
+        <v>16.7</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>12.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>18.8</v>
+        <v>25.5</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>18.4</v>
+        <v>89.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>746.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>20.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>78.5</v>
+        <v>8383.6</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>22.4</v>
+        <v>4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2827,43 +2793,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>343.6</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>21.9</v>
+        <v>453.6</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4007
+263
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="8" t="n">
+        <v>41.4</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>149.9</v>
+        <v>14.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>5.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.9</v>
+        <v>26.9</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="M29" s="3" t="n">
-        <v>15</v>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6041
+151
+</t>
+        </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>84.8</v>
+        <v>584</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>3.1</v>
@@ -2871,29 +2843,29 @@
       <c r="Q29" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>12.7</v>
+      <c r="R29" s="8" t="n">
+        <v>727.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>61.2</v>
+        <v>74.7</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>20.8</v>
+        <v>1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>18.8</v>
+        <v>16.4</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>18.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>88</v>
+        <v>75.2</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>5</v>
@@ -2912,22 +2884,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>178.8</v>
+        <v>343.6</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>121.1</v>
+        <v>13.7</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>21.4</v>
+        <v>6.4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>70.7</v>
+        <v>7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>2.8</v>
@@ -2936,49 +2908,49 @@
         <v>4.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>16.8</v>
+        <v>55.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>86.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>21</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>22</v>
+        <v>228</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>109.4</v>
+        <v>4.6</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1.2</v>
+        <v>81.5</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>161.8</v>
+        <v>20.8</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>91.8</v>
+        <v>18.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>20.9</v>
+        <v>26.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>2.8</v>
@@ -2997,76 +2969,80 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2357.7</v>
+        <v>1788.4</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>22.6</v>
+        <v>26.3</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>5111.1</v>
-      </c>
-      <c r="H31" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I31" s="8" t="n">
-        <v>83</v>
+      <c r="I31" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <v>29.7</v>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 3
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N31" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n">
+        <v>4584.5</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 48
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="O31" s="3" t="n">
-        <v>8543.1</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>19.1</v>
+      <c r="S31" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>20.4</v>
+        <v>0.2</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>18.4</v>
+        <v>91.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>83.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3082,19 +3058,23 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>266.6</v>
+        <v>35.7</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>26.7</v>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+77
+</t>
+        </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>13.4</v>
@@ -3105,53 +3085,53 @@
       <c r="J32" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>681.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+777
+</t>
+        </is>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>18.3</v>
+        <v>22.8</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>20.4</v>
+        <v>49.1</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>978</v>
+        <v>8.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>17.5</v>
+        <v>0.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>20.6</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="X32" s="3" t="n"/>
       <c r="Y32" s="3" t="n">
-        <v>94</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3167,15 +3147,15 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1400.8</v>
+        <v>266.6</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>26.4</v>
+        <v>7.3</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F33" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3187,56 +3167,52 @@
       <c r="I33" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K33" s="8" t="n">
-        <v>29.7</v>
-      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>4.5</v>
+        <v>15.7</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>1.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>61.6</v>
       </c>
       <c r="Q33" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>19.8</v>
-      </c>
       <c r="T33" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W33" s="8" t="n">
-        <v>28</v>
+        <v>17.5</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>12.7</v>
+        <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.8</v>
+        <v>946.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>30.2</v>
+        <v>12.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3252,73 +3228,75 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1250.2</v>
+        <v>406.8</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>27.3</v>
+        <v>24.8</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>20.9</v>
+        <v>41.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H34" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="I34" s="8" t="n">
-        <v>12</v>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7777
+262
+</t>
+        </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>15.8</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n">
-        <v>17.1</v>
+        <v>12.1</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.8</v>
+        <v>13.2</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>78</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>23.3</v>
+        <v>21.4</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.4</v>
+        <v>19.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>74.8</v>
+        <v>7.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>20.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>20.6</v>
+        <v>18.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3337,7 +3315,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>268.8</v>
+        <v>35.6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>24.8</v>
@@ -3346,67 +3324,65 @@
         <v>16.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="I35" s="8" t="n">
-        <v>12</v>
+      <c r="I35" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10.8</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>820</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>22.8</v>
+        <v>0.5</v>
       </c>
       <c r="R35" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S35" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="S35" s="3" t="n">
-        <v>21.1</v>
-      </c>
       <c r="T35" s="3" t="n">
-        <v>76</v>
+        <v>4.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>13.9</v>
+        <v>7.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>20.1</v>
+        <v>10.7</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1.1</v>
+        <v>60.6</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3422,76 +3398,70 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>356.8</v>
+        <v>468.8</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>48.4</v>
+        <v>20.7</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>14.9</v>
+        <v>2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>15.4</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>898</v>
+        <v>800.6</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>14.3</v>
+        <v>4</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>964.1</v>
+        <v>22.8</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>80.8</v>
+        <v>76</v>
+      </c>
+      <c r="U36" s="3" t="n"/>
+      <c r="V36" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>19.8</v>
+        <v>18.9</v>
       </c>
       <c r="X36" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="Z36" s="3" t="n">
         <v>0.6</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>1.1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3507,71 +3477,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>164.3</v>
+        <v>35.8</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>137.7</v>
+        <v>17.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>89.2</v>
+        <v>8.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
+        <v>22.1</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.5</v>
+        <v>1.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.5</v>
+        <v>31.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>736.1</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>88.3</v>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>898</v>
+        <v>7</v>
       </c>
       <c r="P37" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>961.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>99.09999999999999</v>
-      </c>
       <c r="S37" s="3" t="n">
-        <v>3.8</v>
+        <v>21.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>289.4</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>6.2</v>
+      </c>
+      <c r="U37" s="3" t="n"/>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+2248
+</t>
+        </is>
       </c>
       <c r="W37" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>111.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+181 1
+</t>
+        </is>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>0.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>1.8</v>
@@ -3590,73 +3564,78 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>86.3</v>
+        <v>643.2</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>63.7</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>97</v>
+        <v>8.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="I38" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J38" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1.4</v>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5247
+2272
+1
+</t>
+        </is>
       </c>
       <c r="L38" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P38" s="3" t="n"/>
+        <v>7.8</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q38" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
+      </c>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="n">
+        <v>63.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W38" s="8" t="n">
-        <v>92.09999999999999</v>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14441
+346
+</t>
+        </is>
       </c>
       <c r="X38" s="3" t="n"/>
       <c r="Y38" s="3" t="n">
-        <v>122.9</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3671,65 +3650,65 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>16</v>
+        <v>8.4</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1 23
+</t>
+        </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>20.7</v>
+        <v>41.4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n">
-        <v>20.9</v>
+        <v>2.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>7.6</v>
+        <v>17.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0.6</v>
+        <v>18.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>88</v>
+        <v>10.1</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>13.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>12.5</v>
+      </c>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>80.8</v>
+        <v>7.1</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W39" s="3" t="n">
-        <v>80.90000000000001</v>
+      <c r="W39" s="8" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>18.5</v>
@@ -3737,9 +3716,7 @@
       <c r="Y39" s="3" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="Z39" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3760,19 +3737,15 @@
         <v>25.6</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>3.8</v>
@@ -3780,35 +3753,34 @@
       <c r="K40" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L40" s="3" t="n">
-        <v>43.8</v>
-      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="n">
-        <v>88</v>
+        <v>285.2</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>6</v>
+        <v>162.6</v>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231 1
+</t>
+        </is>
       </c>
       <c r="T40" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>1.2</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20</v>
@@ -3823,7 +3795,7 @@
         <v>89.7</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3839,61 +3811,61 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>359</v>
+        <v>286.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.5</v>
+        <v>29.7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H41" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+111
+</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.6</v>
+        <v>9</v>
+      </c>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S41" s="8" t="n">
-        <v>20.4</v>
+        <v>26.8</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>12.8</v>
+        <v>744.4</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>23.3</v>
@@ -3902,10 +3874,10 @@
         <v>19.6</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>80.5</v>
+        <v>70.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>8.4</v>
@@ -3924,71 +3896,79 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.2</v>
+        <v>359</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>27.6</v>
+        <v>18.3</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G42" s="3" t="n"/>
+        <v>15.6</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>4.3</v>
+      </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n">
-        <v>7.1</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>15.7</v>
+        <v>16.3</v>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+2
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9271249
+157
+</t>
+        </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>31.6</v>
+        <v>6.6</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>3.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>14.1</v>
-      </c>
+        <v>57.9</v>
+      </c>
+      <c r="U42" s="3" t="n"/>
       <c r="V42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
         <v>19.4</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Z42" s="3" t="n"/>
+      <c r="Z42" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4003,63 +3983,79 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>734.5</v>
+        <v>27.6</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="8" t="n">
-        <v>161.5</v>
+        <v>26.7</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="N43" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711797
+127
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+118
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>0.5</v>
+        <v>79.8</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>28.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S43" s="3" t="n"/>
+        <v>22.1</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>77.7</v>
+        <v>55.5</v>
       </c>
       <c r="U43" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>1686.8</v>
       </c>
       <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="W43" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X43" s="3" t="n"/>
       <c r="Y43" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>23.6</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>57.7</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4074,71 +4070,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>26.9</v>
+        <v>0.2</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+60292929572
+</t>
+        </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="8" t="n">
-        <v>92.5</v>
+        <v>77.3</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>69.7</v>
       </c>
-      <c r="I44" s="8" t="n">
-        <v>61.4</v>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1642
+24749414
+</t>
+        </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>26.1</v>
+        <v>2.1</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>90.2</v>
+        <v>7.7</v>
+      </c>
+      <c r="L44" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+118
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>29.1</v>
-      </c>
+        <v>72.7</v>
+      </c>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
       <c r="R44" s="3" t="n">
-        <v>80.8</v>
+        <v>7.1</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>80.8</v>
+        <v>72.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v>556.6</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>21</v>
-      </c>
+        <v>777.3</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V44" s="3" t="n"/>
       <c r="W44" s="3" t="n">
-        <v>18.7</v>
+        <v>98.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>21.7</v>
+        <v>0.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
@@ -4155,69 +4159,85 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>367.9</v>
+        <v>0.1</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>26.9</v>
+        <v>39.7</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>21.6</v>
+        <v>4.6</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>45.1</v>
+        <v>179128.7</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.5</v>
+        <v>17.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.2</v>
+        <v>26.1</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N45" s="3" t="n"/>
+        <v>7.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>34.1</v>
+        <v>52.1</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>29.1</v>
+        <v>25.1</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>80.8</v>
+        <v>262.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>80.8</v>
+        <v>26.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>66</v>
+        <v>0.6</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>1.4</v>
+        <v>463.8</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4224574
+1
+</t>
+        </is>
       </c>
       <c r="W45" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X45" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>4.7</v>
+        <v>0.1</v>
       </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4234,51 +4254,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817857
+1 1
+1
+3
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H46" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N46" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>11.1</v>
+      </c>
+      <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
       <c r="U46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V46" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>18.9</v>
+      </c>
       <c r="W46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>11.1</v>
+        <v>6.2</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1
+</t>
+        </is>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.6</v>
+        <v>114.5</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,52 +736,56 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2389.8</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>28.3</v>
+        <v>389.8</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="J4" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M4" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>195.1</v>
+      <c r="N4" s="8" t="n">
+        <v>88.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S4" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="T4" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
@@ -789,7 +793,7 @@
         <v>4.3</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>820.8</v>
+        <v>20.3</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.7</v>
@@ -798,10 +802,10 @@
         <v>20.6</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>286.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>3.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -817,63 +821,67 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1428.6</v>
+        <v>438.6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>28.2</v>
+        <v>22.2</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+        <v>28.5</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>2214.4</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="8" t="n">
+      <c r="K5" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="M5" s="3" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>193.1</v>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>1101.2</v>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>13.1</v>
+        <v>84.3</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.4</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>19.1</v>
@@ -881,9 +889,7 @@
       <c r="Y5" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z5" s="3" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="Z5" s="3" t="inlineStr"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -901,49 +907,53 @@
         <v>484.4</v>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>26.9</v>
+      <c r="E6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>10.7</v>
+        <v>15.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="M6" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>65.09999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q6" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>20.3</v>
+      <c r="R6" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>6.4</v>
+        <v>69</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>10.9</v>
@@ -951,17 +961,17 @@
       <c r="V6" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>91</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -976,18 +986,20 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>28.2</v>
+      <c r="C7" s="3" t="n">
+        <v>274.4</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>54.2</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>20.2</v>
+      <c r="F7" s="3" t="n">
+        <v>61.5</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>12</v>
+        <v>1.1</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>12.8</v>
@@ -995,18 +1007,18 @@
       <c r="I7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="8" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>69.8</v>
+      <c r="L7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>89.8</v>
@@ -1014,19 +1026,25 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="Q7" s="8" t="n">
+        <v>88.2</v>
+      </c>
       <c r="R7" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="T7" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="U7" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V7" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1036,7 +1054,7 @@
         <v>90</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>12.5</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1051,18 +1069,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="n">
+        <v>1260.2</v>
+      </c>
       <c r="D8" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>82.09999999999999</v>
+      <c r="F8" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1071,10 +1091,10 @@
         <v>2.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>17</v>
@@ -1083,27 +1103,31 @@
         <v>15.8</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>88.2</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>24.5</v>
+      </c>
       <c r="R8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>26.8</v>
+      </c>
       <c r="T8" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>9.6</v>
+        <v>29.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>18</v>
@@ -1130,54 +1154,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>829.1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>112.4</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>259.8</v>
+        <v>39.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>722.1</v>
+        <v>61.7</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>22.8</v>
+        <v>221.8</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>116.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>31</v>
+        <v>81.8</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>84.5</v>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>212.3</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>34220.1</v>
+        <v>22</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
+        <v>9.4</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>412.4</v>
+      </c>
       <c r="T9" s="3" t="n">
         <v>384.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1938.5</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>28.5</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>928.9</v>
+      </c>
       <c r="W9" s="3" t="n">
-        <v>927103.1</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>1120.1</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>19445.1</v>
+        <v>9445.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>12.8</v>
@@ -1198,46 +1242,72 @@
       <c r="C10" s="3" t="n">
         <v>428.1</v>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="F10" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>22.9</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>141.1</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>22017.1</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>821.1</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>906.1</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>76.8</v>
+      </c>
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="n">
+        <v>89.8</v>
+      </c>
       <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr"/>
-      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="Z10" s="3" t="n">
-        <v>25.1</v>
+        <v>215.1</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1253,70 +1323,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1299.6</v>
-      </c>
-      <c r="D11" s="8" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>21.7</v>
+        <v>28.1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>21.7</v>
+        <v>24.1</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>5.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>416.8</v>
+        <v>10.4</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>66</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="U11" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W11" s="3" t="n">
+      <c r="V11" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="W11" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>84.5</v>
+      </c>
       <c r="Z11" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1332,19 +1408,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2343.6</v>
+        <v>343.6</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>17.8</v>
+        <v>87.8</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>29.1</v>
+        <v>9.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>15</v>
@@ -1353,10 +1429,10 @@
         <v>2.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>28.4</v>
+        <v>8.4</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.4</v>
@@ -1364,42 +1440,44 @@
       <c r="M12" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="N12" s="8" t="n">
-        <v>3.6</v>
+      <c r="N12" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>192.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.6</v>
+        <v>16.6</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.9</v>
+        <v>22.2</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Y12" s="3" t="inlineStr"/>
+        <v>20.2</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
       <c r="Z12" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1493,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2323.8</v>
+        <v>29323.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>27.5</v>
@@ -1426,32 +1504,34 @@
       <c r="F13" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="I13" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.1</v>
+        <v>87.7</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.8</v>
+        <v>14.8</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>92.2</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>16.4</v>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="n">
+        <v>24.4</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>21.4</v>
@@ -1460,7 +1540,7 @@
         <v>23.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>16.8</v>
@@ -1468,17 +1548,17 @@
       <c r="V13" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>99.40000000000001</v>
+      <c r="W13" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>10.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1494,43 +1574,49 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>260</v>
+        <v>8600.4</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>48.4</v>
+        <v>17.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="I14" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="J14" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="8" t="n">
-        <v>18.3</v>
+      <c r="J14" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N14" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N14" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>20.5</v>
@@ -1539,10 +1625,10 @@
         <v>23.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>195.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>16.1</v>
+        <v>1.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>19.7</v>
@@ -1551,11 +1637,13 @@
         <v>19.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y14" s="3" t="inlineStr"/>
+        <v>22.5</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="Z14" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1571,7 +1659,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2334.8</v>
+        <v>934.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>28.3</v>
@@ -1580,24 +1668,28 @@
         <v>16.6</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="8" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>18.5</v>
@@ -1606,35 +1698,37 @@
         <v>94</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R15" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R15" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>199.3</v>
-      </c>
-      <c r="U15" s="8" t="n">
+        <v>995.3</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="X15" s="8" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>91</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1650,10 +1744,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>10161.8</v>
+        <v>268.8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>134.8</v>
+        <v>1428.1</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>82</v>
@@ -1662,53 +1756,61 @@
         <v>109.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1481.4</v>
+        <v>481.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>72</v>
+        <v>190.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>110.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.9</v>
+        <v>114.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>11812.6</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="n">
+        <v>85.3</v>
+      </c>
       <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>8653.1</v>
+        <v>1465.9</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>311.4</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>419.6</v>
+        <v>9920.799999999999</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>13359.1</v>
+        <v>35.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1101.8</v>
+        <v>101.8</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>109.7</v>
+        <v>108.7</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>457.4</v>
+        <v>4658.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>10.4</v>
@@ -1726,46 +1828,76 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>911.3</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="C17" s="3" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>11.1</v>
+      </c>
       <c r="Q17" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr"/>
+      <c r="R17" s="8" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>788.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="V17" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="inlineStr"/>
-      <c r="Z17" s="3" t="inlineStr"/>
+        <v>29.4</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1780,13 +1912,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>954.6</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>27.1</v>
+        <v>2954.6</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>20.9</v>
@@ -1795,46 +1927,58 @@
         <v>16.7</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="L18" s="8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>88.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q18" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="R18" s="8" t="n">
-        <v>12.8</v>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="T18" s="3" t="inlineStr"/>
+        <v>22.8</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>16.5</v>
+      </c>
       <c r="U18" s="8" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr"/>
+        <v>4148.7</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>26.7</v>
+      </c>
       <c r="Y18" s="3" t="n">
-        <v>83.5</v>
+        <v>80</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>14.1</v>
@@ -1852,39 +1996,47 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="n">
+        <v>119.4</v>
+      </c>
       <c r="D19" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>21.8</v>
+      <c r="F19" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+        <v>21.2</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>2.3</v>
+        <v>25.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>27.9</v>
+      <c r="M19" s="8" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>8.9</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P19" s="3" t="n">
-        <v>12.2</v>
+      <c r="P19" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>23.8</v>
@@ -1892,25 +2044,29 @@
       <c r="R19" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="T19" s="3" t="inlineStr"/>
+      <c r="S19" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>13.1</v>
+      </c>
       <c r="U19" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W19" s="3" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="X19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>13.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1925,35 +2081,47 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>53.4</v>
+      </c>
       <c r="D20" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>21.9</v>
+      </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr"/>
+        <v>21.2</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>22.8</v>
@@ -1964,22 +2132,26 @@
       <c r="S20" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="8" t="n">
-        <v>23.1</v>
+      <c r="T20" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X20" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>93.8</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -1995,10 +2167,10 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1284.8</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>28.1</v>
+        <v>1824.6</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>1.8</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>17</v>
@@ -2006,23 +2178,33 @@
       <c r="F21" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="G21" s="8" t="n">
+        <v>71.09999999999999</v>
+      </c>
       <c r="H21" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K21" s="3" t="n">
-        <v>23.5</v>
+        <v>3.5</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="N21" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="P21" s="3" t="n">
         <v>18.2</v>
       </c>
@@ -2032,27 +2214,29 @@
       <c r="R21" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S21" s="8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="8" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V21" s="8" t="n">
+      <c r="S21" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W21" s="8" t="n">
-        <v>20.6</v>
+      <c r="W21" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2068,7 +2252,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2339.2</v>
+        <v>339.2</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>27.6</v>
@@ -2080,35 +2264,37 @@
         <v>22.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>10.8</v>
+        <v>106.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>21.6</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>16.2</v>
+        <v>4.2</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>21.4</v>
+      </c>
       <c r="O22" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.5</v>
+        <v>25.1</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>21.5</v>
@@ -2117,16 +2303,16 @@
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>19</v>
+        <v>23.6</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>219</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.6</v>
@@ -2135,7 +2321,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2150,56 +2336,76 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>516.1</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>74.8</v>
+        <v>14.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1121.2</v>
+        <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>169.9</v>
+        <v>129.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>889.4</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>1469.1</v>
+        <v>269.1</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>8115.8</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>393.8</v>
+        <v>299.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>2399.2</v>
+        <v>99.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>110.3</v>
-      </c>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
-      <c r="Y23" s="3" t="inlineStr"/>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>406.8</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>122.9</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2217,69 +2423,69 @@
         <v>2309.7</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>24.7</v>
+        <v>27.5</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>17.4</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F24" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1805.1</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="M24" s="8" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>938.1</v>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>22.2</v>
+      <c r="Q24" s="8" t="n">
+        <v>39.1</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S24" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="T24" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>28.1</v>
-      </c>
       <c r="W24" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="X24" s="3" t="inlineStr"/>
-      <c r="Y24" s="3" t="n">
-        <v>713</v>
-      </c>
+        <v>29.9</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>1183.4</v>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
-        <v>16.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2294,73 +2500,77 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>279.8</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>20.3</v>
+        <v>21.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>22.9</v>
+        <v>7.9</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>89.5</v>
+        <v>11.9</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.1</v>
+        <v>2.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>88.8</v>
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>22.7</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S25" s="3" t="inlineStr"/>
+        <v>20.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V25" s="8" t="n">
-        <v>20.6</v>
+      <c r="V25" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>22.4</v>
+        <v>18.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2376,66 +2586,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>370</v>
+        <v>341.4</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>26.8</v>
+        <v>24.8</v>
       </c>
       <c r="E26" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="8" t="n">
+        <v>82.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
       <c r="U26" s="3" t="n">
-        <v>9.9</v>
+        <v>4.7</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W26" s="3" t="inlineStr"/>
-      <c r="X26" s="8" t="n">
-        <v>14.1</v>
+        <v>20.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>16</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2451,66 +2671,76 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1453.6</v>
+        <v>370</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>51.8</v>
+        <v>46.1</v>
       </c>
       <c r="F27" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="R27" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>206.8</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
-      <c r="T27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>636.4</v>
+      </c>
       <c r="U27" s="3" t="n">
-        <v>6.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
+        <v>20.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="X27" s="3" t="n">
-        <v>12.1</v>
+        <v>20.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>78.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2526,72 +2756,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2343.6</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>116</v>
+        <v>453.6</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.8</v>
+        <v>93.3</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>18.6</v>
+        <v>28.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.9</v>
+        <v>26.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="O28" s="3" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>84</v>
+      </c>
       <c r="P28" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Q28" s="8" t="n">
-        <v>292</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S28" s="8" t="n">
-        <v>3811.6</v>
-      </c>
-      <c r="T28" s="3" t="inlineStr"/>
+        <v>17.8</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="U28" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>20.8</v>
+        <v>6.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X28" s="8" t="n">
-        <v>20.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>88</v>
+        <v>78.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>10.8</v>
+        <v>2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2607,59 +2841,73 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1788.4</v>
+        <v>343.6</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+        <v>26.5</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>21.4</v>
+      </c>
       <c r="G29" s="3" t="n">
-        <v>50</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>702.3</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>63</v>
+        <v>14</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>4.8</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>81.8</v>
+        <v>15.5</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="n">
-        <v>454.5</v>
-      </c>
+      <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>81.59999999999999</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>392.2</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>11.8</v>
+        <v>81.5</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="X29" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y29" s="3" t="n">
-        <v>12008</v>
-      </c>
-      <c r="Z29" s="3" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2673,38 +2921,76 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>186.9</v>
+      </c>
       <c r="D30" s="3" t="n">
-        <v>8010.1</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+        <v>24.4</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>20</v>
+      </c>
       <c r="H30" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
+        <v>700.9</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>893.9</v>
+      </c>
       <c r="M30" s="3" t="n">
-        <v>10181.1</v>
-      </c>
-      <c r="N30" s="3" t="inlineStr"/>
-      <c r="O30" s="3" t="inlineStr"/>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>1424.9</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>111.2</v>
+      </c>
       <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="inlineStr"/>
-      <c r="W30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="n">
+        <v>8109.4</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>222.2</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>91.8</v>
+      </c>
       <c r="X30" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>999.8</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>120</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2719,70 +3005,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1266.6</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>4.6</v>
+        <v>2357.7</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>286.2</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>19.1</v>
+        <v>16.3</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>21.5</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>1100.1</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>82.2</v>
+        <v>14.1</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>120810.1</v>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>792</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>20.4</v>
+        <v>22.8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>98</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.7</v>
+        <v>61.1</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>17.5</v>
+        <v>10.4</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>16.9</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>18.9</v>
+        <v>10</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>1940.6</v>
+        <v>83.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.2</v>
+        <v>40.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2798,60 +3088,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1400.8</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F32" s="8" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F32" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>11.1</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>89.40000000000001</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>1.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>15.4</v>
+      </c>
       <c r="N32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>12.9</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="P32" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>206.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>279.4</v>
+        <v>91</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>5.7</v>
+        <v>10.4</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="n">
-        <v>12.7</v>
+        <v>17.5</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>8.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>86.5</v>
+        <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>29.2</v>
+        <v>182</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -2867,60 +3173,76 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1350.2</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
+        <v>1400.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>29.7</v>
+        <v>24.1</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>17.1</v>
+      </c>
       <c r="M33" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="P33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q33" s="3" t="inlineStr"/>
+        <v>14.8</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>18.4</v>
+      </c>
       <c r="R33" s="3" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>11.8</v>
+        <v>19.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>74.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W33" s="3" t="inlineStr"/>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>84</v>
+        <v>86.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>293.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -2936,57 +3258,77 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1268.8</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
+        <v>2350.2</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="E34" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="8" t="n">
+        <v>11.9</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
+        <v>91.8</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Q34" s="3" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>28.1</v>
+        <v>21.4</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>86</v>
+        <v>74.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="W34" s="3" t="inlineStr"/>
+        <v>7.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X34" s="3" t="n">
-        <v>8.1</v>
+        <v>20.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3001,62 +3343,76 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1356.8</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr"/>
+        <v>268.8</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="G35" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="I35" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
-        <v>26.7</v>
+        <v>22.8</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>6.8</v>
+        <v>19.1</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>160.2</v>
+        <v>86</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.9</v>
+        <v>1.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Y35" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>89.2</v>
+      </c>
       <c r="Z35" s="3" t="n">
-        <v>1.1</v>
+        <v>244.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3071,58 +3427,76 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>28.1</v>
+      </c>
       <c r="E36" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>107.1</v>
+        <v>16</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>710.6</v>
+        <v>12.1</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>166.7</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>60.6</v>
+        <v>1.9</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>88.3</v>
+        <v>17.1</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>18</v>
+        <v>14.6</v>
       </c>
       <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>18298</v>
-      </c>
-      <c r="P36" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T36" s="3" t="n">
-        <v>20859.4</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W36" s="3" t="inlineStr"/>
-      <c r="X36" s="3" t="inlineStr"/>
-      <c r="Y36" s="3" t="inlineStr"/>
-      <c r="Z36" s="3" t="inlineStr"/>
+        <v>60.2</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3136,48 +3510,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>1640.2</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1621.1</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1301.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H37" s="3" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>1600.6</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>86</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>796.1</v>
+        <v>298</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>4.2</v>
+        <v>180.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>22.8</v>
+        <v>122.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>19.4</v>
+        <v>146.1</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T37" s="3" t="inlineStr"/>
-      <c r="U37" s="3" t="inlineStr"/>
+        <v>100.8</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>680.5</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>194.2</v>
+      </c>
       <c r="V37" s="3" t="n">
-        <v>29.6</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>206.1</v>
-      </c>
+        <v>921.2</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>89.7</v>
+        <v>4481.7</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3193,62 +3591,72 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
-        <v>12264.4</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="n">
-        <v>13.2</v>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="8" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>23.1</v>
+      </c>
       <c r="K38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M38" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>15.4</v>
+      </c>
       <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>185</v>
+        <v>796.1</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>93</v>
+        <v>4.2</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>28.2</v>
+        <v>12.2</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>117.8</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="3" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>771.1</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>46.4</v>
+      </c>
       <c r="V38" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="X38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W38" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="n">
-        <v>211.4</v>
-      </c>
+      <c r="X38" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3263,23 +3671,23 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1286.4</v>
+        <v>286.4</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>956.4</v>
+        <v>25.6</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>80.7</v>
+        <v>1.8</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>3.8</v>
@@ -3288,44 +3696,40 @@
         <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>87.7</v>
+        <v>7.7</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>11.1</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>846.6</v>
-      </c>
-      <c r="P39" s="8" t="n">
-        <v>23.6</v>
+        <v>88.5</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>3.6</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>19.5</v>
+      <c r="R39" s="8" t="n">
+        <v>20.9</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X39" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="X39" s="3" t="inlineStr"/>
       <c r="Y39" s="3" t="inlineStr"/>
-      <c r="Z39" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3340,40 +3744,44 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>12359</v>
+        <v>5359</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="F40" s="8" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="n">
+        <v>85.90000000000001</v>
+      </c>
       <c r="J40" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
       <c r="L40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="8" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3388,17 +3796,21 @@
       <c r="U40" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V40" s="8" t="n">
-        <v>1.2</v>
+      <c r="V40" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Y40" s="3" t="inlineStr"/>
-      <c r="Z40" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3413,33 +3825,43 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1486.6</v>
+        <v>8866.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="J41" s="3" t="n">
-        <v>6.3</v>
+        <v>16.3</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>26</v>
       </c>
@@ -3449,21 +3871,25 @@
       <c r="S41" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="T41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="n">
+        <v>57.9</v>
+      </c>
       <c r="U41" s="3" t="n">
-        <v>16.8</v>
+        <v>14.1</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="W41" s="3" t="inlineStr"/>
       <c r="X41" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="Y41" s="3" t="inlineStr"/>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3478,52 +3904,60 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1942.6</v>
+        <v>942.6</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>27.6</v>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="n">
-        <v>1.4</v>
+      <c r="E42" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>1.9</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="H42" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="8" t="n">
-        <v>92.8</v>
+      <c r="J42" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M42" s="8" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
-      <c r="O42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>79.8</v>
+      </c>
       <c r="P42" s="3" t="n">
-        <v>4.2</v>
+        <v>14.2</v>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>78.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>19.9</v>
+      <c r="S42" s="8" t="n">
+        <v>29.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="U42" s="3" t="inlineStr"/>
+        <v>55.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V42" s="3" t="n">
         <v>22.2</v>
       </c>
@@ -3531,12 +3965,14 @@
         <v>18.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>19.7</v>
+        <v>89.7</v>
       </c>
       <c r="Y42" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z42" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3551,53 +3987,69 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>52.5</v>
+      <c r="D43" s="3" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>21.1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>17.4</v>
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>61.9</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>68.09999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="n">
-        <v>1205.5</v>
-      </c>
-      <c r="P43" s="8" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="P43" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="3" t="inlineStr"/>
+      <c r="Q43" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>53.6</v>
+      </c>
       <c r="V43" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+      <c r="W43" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>2011</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>22</v>
+        <v>406.7</v>
       </c>
       <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -3613,7 +4065,9 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
@@ -3651,20 +4105,22 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2368.9</v>
+        <v>362.9</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
+        <v>21.6</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H45" s="3" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>9.5</v>
@@ -3672,31 +4128,51 @@
       <c r="J45" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>15.9</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>16.4</v>
+        <v>11.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>29.9</v>
+        <v>9.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>25.1</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
-      <c r="Y45" s="3" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -3712,35 +4188,65 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="H46" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>410.7</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="Q46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>28.5</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -739,16 +739,16 @@
         <v>389.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E4" s="8" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12.5</v>
+        <v>82.5</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>12.5</v>
@@ -760,10 +760,10 @@
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>16.8</v>
@@ -775,7 +775,7 @@
         <v>90</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>23.7</v>
@@ -783,7 +783,7 @@
       <c r="R4" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>25</v>
       </c>
       <c r="T4" s="3" t="n">
@@ -792,8 +792,8 @@
       <c r="U4" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="V4" s="8" t="n">
-        <v>20.3</v>
+      <c r="V4" s="3" t="n">
+        <v>80.3</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.7</v>
@@ -805,7 +805,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>33.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.6</v>
+        <v>9432.6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>22.2</v>
+        <v>4.9</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>16.9</v>
@@ -833,10 +833,10 @@
         <v>28.5</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>2214.4</v>
+        <v>215</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>21.1</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -844,20 +844,20 @@
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>87.59999999999999</v>
+      <c r="M5" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>11.4</v>
@@ -865,14 +865,14 @@
       <c r="Q5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>84.3</v>
+        <v>74.3</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>81.09999999999999</v>
@@ -932,14 +932,12 @@
         <v>17.2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>92</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="n">
         <v>1.6</v>
       </c>
@@ -987,19 +985,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>274.4</v>
+        <v>384.4</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>54.2</v>
+        <v>28.1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>61.5</v>
+        <v>22.2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>12.8</v>
@@ -1007,7 +1005,9 @@
       <c r="I7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="K7" s="3" t="n">
         <v>0.2</v>
       </c>
@@ -1018,16 +1018,16 @@
         <v>17.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89.8</v>
+        <v>0.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>88.2</v>
+      <c r="Q7" s="3" t="n">
+        <v>27.3</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>22.7</v>
@@ -1036,12 +1036,12 @@
         <v>24.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>18.7</v>
+        <v>68.7</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1260.2</v>
+        <v>260.2</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>28.4</v>
@@ -1078,8 +1078,8 @@
       <c r="E8" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>27.1</v>
+      <c r="F8" s="3" t="n">
+        <v>22.7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>11.4</v>
@@ -1091,7 +1091,7 @@
         <v>2.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>4.1</v>
@@ -1103,13 +1103,13 @@
         <v>15.8</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>69.2</v>
+        <v>67.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>24.5</v>
@@ -1126,8 +1126,8 @@
       <c r="U8" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>29.6</v>
+      <c r="V8" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>18</v>
@@ -1155,43 +1155,43 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>140.4</v>
+        <v>3440.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>82</v>
+        <v>1824.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>829.1</v>
+        <v>29.1</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>112.4</v>
+        <v>12.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>39.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>221.8</v>
+        <v>22.8</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>84.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>212.3</v>
+        <v>12.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.4</v>
@@ -1200,31 +1200,29 @@
         <v>127.1</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>412.4</v>
-      </c>
+        <v>91.2</v>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="n">
         <v>384.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>28.5</v>
+        <v>38.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>928.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>12.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1120.1</v>
+        <v>162.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9445.1</v>
+        <v>445.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>12.8</v>
+        <v>122.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1242,53 +1240,53 @@
       <c r="C10" s="3" t="n">
         <v>428.1</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>28.4</v>
+      <c r="D10" s="8" t="n">
+        <v>89.09999999999999</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>22.9</v>
+        <v>8.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>111.8</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I10" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I10" s="8" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>141.1</v>
+        <v>14.6</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>17.9</v>
+        <v>19.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>21.4</v>
+        <v>4.3</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>821.1</v>
+        <v>687.8</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>25.4</v>
+        <v>18.9</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>12.4</v>
+        <v>22.1</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>76.8</v>
@@ -1296,8 +1294,8 @@
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="3" t="n">
-        <v>89.8</v>
+      <c r="V10" s="8" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="W10" s="3" t="inlineStr"/>
       <c r="X10" s="3" t="n">
@@ -1307,7 +1305,7 @@
         <v>89</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>215.1</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1329,49 +1327,49 @@
         <v>26.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.8</v>
+        <v>86.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>5.1</v>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>31.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>81</v>
+        <v>0.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>28.1</v>
+        <v>41.4</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>20.5</v>
+      <c r="R11" s="8" t="n">
+        <v>16.3</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>68.40000000000001</v>
@@ -1380,13 +1378,13 @@
         <v>10.6</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="W11" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>84.5</v>
@@ -1414,10 +1412,10 @@
         <v>26.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>87.8</v>
+        <v>17.8</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>9.1</v>
@@ -1432,7 +1430,7 @@
         <v>8.4</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.4</v>
+        <v>28.4</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.4</v>
@@ -1444,22 +1442,22 @@
         <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>16.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>22.2</v>
+        <v>8.6</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>93</v>
+        <v>923</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>1.6</v>
@@ -1470,14 +1468,14 @@
       <c r="W12" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>12.9</v>
+      <c r="X12" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>89.09999999999999</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1493,13 +1491,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>29323.8</v>
+        <v>2323.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.3</v>
@@ -1515,20 +1513,18 @@
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="M13" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>92.2</v>
-      </c>
+        <v>13.8</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="3" t="n">
         <v>24.4</v>
@@ -1540,18 +1536,18 @@
         <v>23.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X13" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1574,7 +1570,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8600.4</v>
+        <v>260</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>24.8</v>
@@ -1586,34 +1582,34 @@
         <v>21.1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>11.8</v>
+        <v>14.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>18.2</v>
+      <c r="J14" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="N14" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N14" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>21</v>
@@ -1628,7 +1624,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>19.7</v>
@@ -1640,7 +1636,7 @@
         <v>22.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>0.7</v>
@@ -1659,7 +1655,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>934.8</v>
+        <v>234.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>28.3</v>
@@ -1668,16 +1664,16 @@
         <v>16.6</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2.9</v>
+        <v>22.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>144.1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>21.1</v>
+        <v>2.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
@@ -1689,7 +1685,7 @@
         <v>17.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>10.6</v>
+        <v>16.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>18.5</v>
@@ -1710,22 +1706,22 @@
         <v>21.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>995.3</v>
+        <v>59.3</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="X15" s="8" t="n">
-        <v>2.3</v>
+      <c r="X15" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>10</v>
@@ -1744,10 +1740,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>268.8</v>
+        <v>361.8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1428.1</v>
+        <v>14.6</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>82</v>
@@ -1756,61 +1752,59 @@
         <v>109.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>481.4</v>
+        <v>2481.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190.8</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>110.8</v>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>114.9</v>
-      </c>
+      <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>88.8</v>
+        <v>68.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>85.3</v>
+        <v>83.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1465.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>16.9</v>
+        <v>7160.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>311.4</v>
+        <v>112.9</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>9920.799999999999</v>
+        <v>41.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>35.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>101.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>108.7</v>
+        <v>10.9</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>4658.4</v>
+        <v>458.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>10.4</v>
@@ -1832,41 +1826,41 @@
         <v>312.4</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>81.59999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>2011.7</v>
+        <v>17.1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>28.1</v>
+        <v>481.6</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>19</v>
+      <c r="N17" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>93.2</v>
       </c>
-      <c r="P17" s="8" t="n">
-        <v>11.1</v>
+      <c r="P17" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.9</v>
@@ -1878,7 +1872,7 @@
         <v>29.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>788.4</v>
+        <v>188.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
@@ -1886,17 +1880,17 @@
       <c r="V17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="8" t="n">
         <v>29.4</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>91.5</v>
+        <v>21.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>21.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1912,61 +1906,59 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2954.6</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>77.09999999999999</v>
+        <v>254.6</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>27.7</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="8" t="n">
-        <v>16.7</v>
+        <v>86.7</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>3</v>
+        <v>50.6</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="L18" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>88.3</v>
+      <c r="M18" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>18.6</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S18" s="8" t="n">
-        <v>22.8</v>
+        <v>849.1</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>16.5</v>
+        <v>166.5</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>4148.7</v>
+        <v>41.8</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>20.9</v>
@@ -1974,14 +1966,14 @@
       <c r="W18" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="X18" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1997,7 +1989,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>119.4</v>
+        <v>19.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>27.4</v>
@@ -2006,37 +1998,37 @@
         <v>16.2</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>21.2</v>
+        <v>11.2</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>14.6</v>
+        <v>12.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>25.3</v>
+        <v>2.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>87.40000000000001</v>
+      <c r="M19" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>21.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>23.8</v>
@@ -2044,14 +2036,14 @@
       <c r="R19" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S19" s="8" t="n">
-        <v>8</v>
+      <c r="S19" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>23.4</v>
@@ -2066,7 +2058,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>7.1</v>
+        <v>21.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2081,20 +2073,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>53.4</v>
-      </c>
+      <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>16</v>
@@ -2102,20 +2090,20 @@
       <c r="I20" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J20" s="8" t="n">
-        <v>21.9</v>
+      <c r="J20" s="3" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>18.2</v>
+        <v>49.1</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2129,12 +2117,10 @@
       <c r="R20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>24</v>
-      </c>
+      <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
       </c>
@@ -2167,10 +2153,10 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1824.6</v>
+        <v>1254.6</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>17</v>
@@ -2178,29 +2164,29 @@
       <c r="F21" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="G21" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>68</v>
+        <v>23.5</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>28.9</v>
+        <v>28</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2218,10 +2204,10 @@
         <v>28.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>22</v>
@@ -2264,16 +2250,16 @@
         <v>22.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>106.2</v>
+        <v>10.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>4.2</v>
+        <v>16.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2285,10 +2271,10 @@
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.7</v>
@@ -2299,20 +2285,20 @@
       <c r="R22" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>219</v>
+        <v>23.1</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.6</v>
@@ -2321,7 +2307,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2336,17 +2322,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>36.4</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>21.6</v>
+        <v>7.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.1</v>
+        <v>11.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>92.59999999999999</v>
@@ -2358,54 +2342,52 @@
         <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>129.9</v>
+        <v>129</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.6</v>
+        <v>60.6</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>907.6</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>269.1</v>
+        <v>46.9</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>62</v>
+        <v>6.5</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>18.8</v>
+        <v>24.8</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>8115.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>299.1</v>
+        <v>393.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>99.2</v>
+        <v>93.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>110</v>
+        <v>110.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>199.6</v>
+        <v>28.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>210</v>
+        <v>771.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>406.8</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>122.9</v>
-      </c>
+        <v>41.6</v>
+      </c>
+      <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2420,27 +2402,27 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2309.7</v>
+        <v>309.7</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="E24" s="8" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>1805.1</v>
-      </c>
-      <c r="H24" s="8" t="n">
+      <c r="E24" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I24" s="8" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="J24" s="3" t="n">
+      <c r="I24" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J24" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
@@ -2451,7 +2433,7 @@
         <v>74.09999999999999</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>938.1</v>
@@ -2465,27 +2447,27 @@
       <c r="R24" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="S24" s="8" t="n">
-        <v>32.1</v>
+      <c r="S24" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>18.2</v>
+        <v>874.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>29.9</v>
+        <v>19.9</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>1183.4</v>
+        <v>21183.4</v>
       </c>
       <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2512,20 +2494,14 @@
       <c r="F25" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="L25" s="8" t="n">
         <v>18.8</v>
@@ -2533,20 +2509,18 @@
       <c r="M25" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>94</v>
+        <v>9.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q25" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>22.1</v>
@@ -2567,10 +2541,10 @@
         <v>18.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>6.3</v>
+        <v>16.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2586,7 +2560,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>341.4</v>
+        <v>371.4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>24.8</v>
@@ -2595,43 +2569,43 @@
         <v>15.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="I26" s="8" t="n">
-        <v>25.3</v>
+      <c r="I26" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L26" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L26" s="3" t="n">
         <v>17</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="N26" s="8" t="n">
-        <v>82.8</v>
+      <c r="N26" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R26" s="8" t="n">
-        <v>41.6</v>
+        <v>0.7</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>24.6</v>
@@ -2642,7 +2616,7 @@
       <c r="U26" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2677,7 +2651,7 @@
         <v>26.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46.1</v>
+        <v>4.6</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>21.7</v>
@@ -2686,7 +2660,7 @@
         <v>10.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16</v>
+        <v>460.5</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2.5</v>
@@ -2695,37 +2669,33 @@
         <v>3.5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>25.1</v>
-      </c>
+        <v>16.1</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="T27" s="3" t="n">
-        <v>636.4</v>
-      </c>
+      <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>20.9</v>
@@ -2737,7 +2707,7 @@
         <v>20.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>838.6</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>14</v>
@@ -2762,43 +2732,43 @@
         <v>28.8</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12.1</v>
+        <v>15.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>93.3</v>
+        <v>3.3</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>28.8</v>
+        <v>5.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>26.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>18</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>84</v>
+        <v>840.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>20.8</v>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>6.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17.8</v>
@@ -2806,23 +2776,21 @@
       <c r="S28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="T28" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>6.8</v>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="8" t="n">
+        <v>62.1</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>26.4</v>
+        <v>26.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>78.5</v>
+        <v>77.5</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>2</v>
@@ -2841,19 +2809,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>343.6</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>26.5</v>
+        <v>2343.6</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>26.3</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>21.4</v>
+        <v>101.4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>14</v>
@@ -2865,16 +2833,18 @@
         <v>4.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>16.6</v>
+        <v>0.9</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>46.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="P29" s="3" t="n">
         <v>2.6</v>
       </c>
@@ -2882,13 +2852,13 @@
         <v>22</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>19.7</v>
+        <v>12.7</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>81.5</v>
+        <v>21.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.8</v>
@@ -2899,8 +2869,8 @@
       <c r="W29" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>20.9</v>
+      <c r="X29" s="8" t="n">
+        <v>6.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>88</v>
@@ -2922,74 +2892,68 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>186.9</v>
+        <v>78.8</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>81.7</v>
-      </c>
+        <v>112.1</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>100.4</v>
+        <v>60.9</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>700.9</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119</v>
+        <v>19.3</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>893.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1424.9</v>
+        <v>0.4</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>111.2</v>
+        <v>42.8</v>
       </c>
       <c r="R30" s="3" t="inlineStr"/>
       <c r="S30" s="3" t="n">
-        <v>8109.4</v>
+        <v>2109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>222.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>30.3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>111.8</v>
+        <v>1681.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>999.8</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>116.1</v>
-      </c>
+        <v>99.90000000000001</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
       <c r="Z30" s="3" t="n">
-        <v>120</v>
+        <v>0.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3007,60 +2971,60 @@
       <c r="C31" s="3" t="n">
         <v>2357.7</v>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>286.2</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>16.3</v>
+      <c r="D31" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>1100.1</v>
+        <v>110</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20.8</v>
+        <v>26.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.9</v>
+        <v>2.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>172.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>120810.1</v>
+        <v>21810.1</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>126.6</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>19.1</v>
+        <v>20</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>61.1</v>
+        <v>6.1</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="W31" s="8" t="n">
         <v>84.09999999999999</v>
@@ -3090,74 +3054,72 @@
       <c r="C32" s="3" t="n">
         <v>266.6</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>29.1</v>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>1.4</v>
+        <v>21</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>18.9</v>
+        <v>6.2</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="R32" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>206.4</v>
+        <v>20.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V32" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V32" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="W32" s="8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X32" s="8" t="n">
-        <v>8.1</v>
+      <c r="W32" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>182</v>
+        <v>21.1</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3173,7 +3135,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1400.8</v>
+        <v>400.8</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>27.3</v>
@@ -3181,21 +3143,19 @@
       <c r="E33" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>24.1</v>
-      </c>
+        <v>8.6</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
         <v>5.8</v>
       </c>
@@ -3203,19 +3163,19 @@
         <v>17.1</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>2.8</v>
+        <v>28.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Q33" s="8" t="n">
-        <v>18.4</v>
+        <v>14.3</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>18.6</v>
@@ -3229,11 +3189,11 @@
       <c r="U33" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V33" s="8" t="n">
-        <v>89.59999999999999</v>
+      <c r="V33" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>12.7</v>
@@ -3242,7 +3202,7 @@
         <v>86.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3273,49 +3233,45 @@
         <v>7.9</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>15.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>39.7</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
       <c r="L34" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="N34" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>91.8</v>
+        <v>98</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>23.3</v>
+        <v>0.7</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>18.8</v>
@@ -3327,7 +3283,7 @@
         <v>84</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3364,7 +3320,7 @@
         <v>2</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3373,13 +3329,13 @@
         <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>45</v>
+        <v>1.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
@@ -3388,7 +3344,7 @@
         <v>22.8</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>21.1</v>
@@ -3397,7 +3353,7 @@
         <v>86</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.1</v>
@@ -3409,10 +3365,10 @@
         <v>21.1</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>89.2</v>
+        <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>244.1</v>
+        <v>21.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3443,13 +3399,13 @@
         <v>12.1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4</v>
@@ -3462,10 +3418,10 @@
       </c>
       <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>26.7</v>
@@ -3474,7 +3430,7 @@
         <v>20.8</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>60.2</v>
@@ -3482,11 +3438,11 @@
       <c r="U36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>20.8</v>
+      <c r="V36" s="8" t="n">
+        <v>80.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>22.6</v>
@@ -3495,7 +3451,7 @@
         <v>95.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3511,71 +3467,69 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1640.2</v>
+        <v>1645.2</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1621.1</v>
+        <v>1182.8</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1301.1</v>
+        <v>1609.1</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>48.5</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>10.6</v>
+        <v>710.6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>106.7</v>
+        <v>116.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1600.6</v>
+        <v>160.6</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="n">
-        <v>86</v>
+        <v>86.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>298</v>
+        <v>228</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>180.8</v>
+        <v>120.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>122.9</v>
+        <v>1812.3</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>146.1</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>100.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>680.5</v>
+        <v>289.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>194.2</v>
+        <v>94.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>921.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>4481.7</v>
+        <v>418.8</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3591,27 +3545,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="8" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>66.09999999999999</v>
+      <c r="C38" s="3" t="n">
+        <v>1292.8</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>634.1</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="H38" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>23.1</v>
+      <c r="J38" s="3" t="n">
+        <v>33.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0.4</v>
@@ -3629,32 +3585,30 @@
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
-        <v>12.2</v>
+      <c r="Q38" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>117.8</v>
+        <v>19.1</v>
       </c>
       <c r="S38" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>771.1</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>46.4</v>
-      </c>
+        <v>77.09999999999999</v>
+      </c>
+      <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" s="3" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>8.6</v>
+        <v>18.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3671,7 +3625,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>286.4</v>
+        <v>986.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>25.6</v>
@@ -3680,7 +3634,7 @@
         <v>15.8</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="n">
@@ -3693,17 +3647,17 @@
         <v>3.8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>7.7</v>
+        <v>80</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>11.1</v>
+        <v>17.1</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>3.6</v>
@@ -3712,10 +3666,10 @@
         <v>22.8</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>20.9</v>
+        <v>22.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>74.40000000000001</v>
@@ -3744,7 +3698,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5359</v>
+        <v>359</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>27.5</v>
@@ -3753,19 +3707,21 @@
         <v>15.6</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>111.6</v>
+        <v>181.6</v>
       </c>
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L40" s="3" t="n">
         <v>18</v>
       </c>
@@ -3776,10 +3732,10 @@
         <v>15.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>86.2</v>
+        <v>76.2</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>25.8</v>
@@ -3791,13 +3747,13 @@
         <v>20.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="U40" s="3" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="U40" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.2</v>
+        <v>0.2</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>19.6</v>
@@ -3809,7 +3765,7 @@
         <v>86.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>32.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3825,7 +3781,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8866.4</v>
+        <v>4866.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>28.3</v>
@@ -3834,35 +3790,35 @@
         <v>17</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.2</v>
+        <v>81.8</v>
       </c>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>16.3</v>
+        <v>6.3</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>27.7</v>
+        <v>17.7</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q41" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3904,7 +3860,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>942.6</v>
+        <v>242.6</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>27.6</v>
@@ -3912,18 +3868,18 @@
       <c r="E42" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>1.9</v>
+      <c r="F42" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
@@ -3934,30 +3890,28 @@
       <c r="M42" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Q42" s="8" t="n">
-        <v>84.09999999999999</v>
+        <v>4.2</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="S42" s="8" t="n">
-        <v>29.9</v>
+        <v>20.2</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>55.5</v>
       </c>
-      <c r="U42" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U42" s="3" t="inlineStr"/>
       <c r="V42" s="3" t="n">
         <v>22.2</v>
       </c>
@@ -3965,10 +3919,10 @@
         <v>18.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>89.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>13.4</v>
+        <v>23.4</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>7.1</v>
@@ -3986,30 +3940,32 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>10.9</v>
+      <c r="C43" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>80.90000000000001</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="G43" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>9.4</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>26.1</v>
+        <v>61.8</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>90.2</v>
@@ -4019,37 +3975,35 @@
       </c>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="n">
-        <v>105.5</v>
+        <v>405.5</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="Q43" s="8" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>10.2</v>
+      <c r="Q43" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>61.6</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>161.6</v>
+        <v>10.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>20</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>53.6</v>
+        <v>55.6</v>
       </c>
       <c r="V43" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="W43" s="3" t="inlineStr"/>
       <c r="X43" s="3" t="n">
-        <v>2011</v>
+        <v>20.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>406.7</v>
+        <v>12</v>
       </c>
       <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -4126,19 +4080,19 @@
         <v>9.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>81.09999999999999</v>
@@ -4147,10 +4101,10 @@
         <v>9.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>25.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>20.8</v>
+        <v>202.8</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>20.8</v>
@@ -4171,7 +4125,7 @@
         <v>20.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4195,19 +4149,19 @@
         <v>0.1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>11.4</v>
+        <v>0.8</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>11.4</v>
+        <v>17.1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>11.4</v>
+        <v>4.6</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>4.8</v>
@@ -4218,35 +4172,31 @@
       <c r="M46" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N46" s="8" t="n">
-        <v>410.7</v>
+      <c r="N46" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>8.6</v>
+        <v>0.2</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
       <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr"/>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -745,10 +745,10 @@
         <v>15.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>22.1</v>
+        <v>28.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>82.5</v>
+        <v>12.5</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>12.5</v>
@@ -765,14 +765,14 @@
       <c r="L4" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>88.5</v>
+      <c r="N4" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2</v>
@@ -783,17 +783,17 @@
       <c r="R4" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>80.3</v>
+        <v>20.3</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.7</v>
@@ -804,9 +804,7 @@
       <c r="Y4" s="3" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="Z4" s="3" t="n">
-        <v>33.6</v>
-      </c>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -821,22 +819,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9432.6</v>
+        <v>438.6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4.9</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>28.5</v>
+        <v>42.5</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>215</v>
+        <v>19.5</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>21.1</v>
+        <v>121</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -844,20 +842,20 @@
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="8" t="n">
-        <v>22.3</v>
+      <c r="K5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>19.7</v>
+        <v>1.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>11.4</v>
@@ -872,10 +870,10 @@
         <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>74.3</v>
+        <v>84.3</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>18</v>
@@ -883,13 +881,15 @@
       <c r="W5" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>484.4</v>
+        <v>494.4</v>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="n">
@@ -916,17 +916,17 @@
       <c r="G6" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>15.2</v>
+      <c r="H6" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>3.8</v>
+        <v>13.8</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>17.2</v>
@@ -935,9 +935,11 @@
         <v>16.4</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O6" s="3" t="inlineStr"/>
+        <v>18.2</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="P6" s="3" t="n">
         <v>1.6</v>
       </c>
@@ -959,17 +961,17 @@
       <c r="V6" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>21.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>91</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -987,9 +989,7 @@
       <c r="C7" s="3" t="n">
         <v>384.4</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>28.1</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
         <v>16.2</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>12.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.8</v>
@@ -1018,10 +1018,10 @@
         <v>17.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>12.8</v>
+        <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.8</v>
+        <v>89.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1036,7 +1036,7 @@
         <v>24.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>68.7</v>
+        <v>18.7</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>11.4</v>
@@ -1048,13 +1048,13 @@
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>22.1</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>2.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>260.2</v>
+        <v>460.2</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>28.4</v>
@@ -1102,14 +1102,14 @@
       <c r="M8" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N8" s="8" t="n">
-        <v>67.2</v>
+      <c r="N8" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>12.2</v>
+        <v>21.2</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>24.5</v>
@@ -1136,10 +1136,10 @@
         <v>19.7</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>86</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>3.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1155,22 +1155,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3440.5</v>
+        <v>2240.4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1824.8</v>
+        <v>142</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>29.1</v>
+        <v>829.1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>259.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.8</v>
+        <v>671.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.2</v>
@@ -1182,27 +1182,27 @@
         <v>16.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>3980.1</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>84.5</v>
       </c>
-      <c r="N9" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>22.1</v>
+        <v>343.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>127.1</v>
+        <v>1272.1</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="S9" s="3" t="inlineStr"/>
+        <v>110.9</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>124.3</v>
+      </c>
       <c r="T9" s="3" t="n">
         <v>384.2</v>
       </c>
@@ -1210,19 +1210,19 @@
         <v>38.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>28.9</v>
       </c>
       <c r="W9" s="3" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>445.1</v>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>12.7</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>162.8</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>445.8</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>122.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1240,64 +1240,64 @@
       <c r="C10" s="3" t="n">
         <v>428.1</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>16.6</v>
+      <c r="D10" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>66.09999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8.5</v>
+        <v>22.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I10" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>19.9</v>
+        <v>1.1</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>687.8</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>18.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>2.9</v>
+        <v>26.4</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>22.1</v>
+        <v>1.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>24.9</v>
+        <v>1041.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>18.5</v>
+      </c>
       <c r="X10" s="3" t="n">
         <v>20.6</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>89</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>2.5</v>
+        <v>161.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1327,26 +1327,24 @@
         <v>26.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>86.8</v>
+        <v>16.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>28.7</v>
+        <v>21.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>17.2</v>
       </c>
@@ -1354,37 +1352,35 @@
         <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>41.4</v>
+        <v>8.5</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P11" s="3" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="S11" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W11" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X11" s="3" t="n">
-        <v>82</v>
+      <c r="X11" s="8" t="n">
+        <v>822</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>84.5</v>
@@ -1427,13 +1423,13 @@
         <v>2.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>18.4</v>
+        <v>2.4</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>81.40000000000001</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>17.6</v>
@@ -1442,7 +1438,7 @@
         <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.6</v>
@@ -1450,14 +1446,14 @@
       <c r="Q12" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>8.6</v>
+      <c r="S12" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>923</v>
+        <v>93</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>1.6</v>
@@ -1469,7 +1465,7 @@
         <v>20.2</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>89.09999999999999</v>
@@ -1491,41 +1487,45 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2323.8</v>
+        <v>323.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="8" t="n">
+        <v>21</v>
+      </c>
       <c r="K13" s="3" t="n">
         <v>14</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q13" s="3" t="n">
         <v>24.4</v>
       </c>
@@ -1536,18 +1536,18 @@
         <v>23.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="X13" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1578,20 +1578,18 @@
       <c r="E14" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>21.1</v>
+      <c r="F14" s="8" t="n">
+        <v>821.1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>22.2</v>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
@@ -1602,8 +1600,8 @@
       <c r="M14" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>18.9</v>
+      <c r="N14" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
@@ -1624,7 +1622,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>19.7</v>
@@ -1633,10 +1631,10 @@
         <v>19.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>0.7</v>
@@ -1655,7 +1653,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>234.8</v>
+        <v>334.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>28.3</v>
@@ -1663,23 +1661,23 @@
       <c r="E15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>22.9</v>
+      <c r="F15" s="8" t="n">
+        <v>8.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.7</v>
+        <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>144.1</v>
+        <v>14.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>24.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>17.2</v>
@@ -1688,7 +1686,7 @@
         <v>16.6</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>18.5</v>
+        <v>11.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>94</v>
@@ -1697,18 +1695,18 @@
         <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>59.3</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="8" t="n">
         <v>16</v>
       </c>
       <c r="V15" s="3" t="n">
@@ -1724,7 +1722,7 @@
         <v>21</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1740,75 +1738,75 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>361.8</v>
+        <v>1361.8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.6</v>
+        <v>134</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>82</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>109.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2481.4</v>
+        <v>481.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>110.8</v>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="K16" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>68.8</v>
+        <v>88.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>83.3</v>
+        <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>1465.9</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>16.9</v>
+        <v>1089.3</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>7160.3</v>
+        <v>104.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>112.9</v>
+        <v>2116.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>41.5</v>
+        <v>199.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>35.1</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>101.8</v>
+        <v>101.9</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>969.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>10.9</v>
+        <v>98.7</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>458.4</v>
       </c>
-      <c r="Z16" s="3" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1823,29 +1821,31 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>312.4</v>
+        <v>2312.4</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>60.1</v>
+        <v>40.1</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>29.7</v>
+      </c>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>481.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>17.8</v>
@@ -1854,40 +1854,40 @@
         <v>17.8</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>14.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>29.8</v>
+        <v>189.1</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>188.7</v>
+        <v>789.1</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>29.4</v>
+      <c r="V17" s="8" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>21.5</v>
+        <v>2812.1</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2.1</v>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>254.6</v>
+        <v>354.6</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>27.7</v>
@@ -1914,30 +1914,32 @@
       <c r="E18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="8" t="n">
-        <v>86.7</v>
+      <c r="F18" s="8" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>50.6</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L18" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L18" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>81.09999999999999</v>
@@ -1946,10 +1948,10 @@
         <v>20.7</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>26.7</v>
+        <v>9.6</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>849.1</v>
+        <v>21.8</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>29.3</v>
@@ -1957,23 +1959,23 @@
       <c r="T18" s="3" t="n">
         <v>166.5</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>41.8</v>
+      <c r="U18" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="V18" s="3" t="n">
+        <v>22488.4</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="X18" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>26.7</v>
-      </c>
       <c r="Y18" s="3" t="n">
-        <v>82</v>
+        <v>118.9</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>4.1</v>
+        <v>20.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1989,7 +1991,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>19.4</v>
+        <v>219.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>27.4</v>
@@ -1997,53 +1999,53 @@
       <c r="E19" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="F19" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="F19" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.6</v>
+        <v>14.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>22.8</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2.3</v>
+        <v>22.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>27.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>88.09999999999999</v>
+      <c r="P19" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>8.9</v>
+        <v>17.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>23.4</v>
@@ -2055,10 +2057,10 @@
         <v>21.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>19.6</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>21.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2073,14 +2075,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="n">
+      <c r="C20" s="3" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="D20" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G20" s="3" t="n">
         <v>9</v>
       </c>
@@ -2088,22 +2094,22 @@
         <v>16</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.9</v>
+        <v>19.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>49.1</v>
+        <v>18.2</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>22.3</v>
+        <v>2.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2117,10 +2123,12 @@
       <c r="R20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="S20" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>1891.8</v>
+      </c>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
       </c>
@@ -2153,10 +2161,10 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1254.6</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>88.09999999999999</v>
+        <v>2284.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>17</v>
@@ -2164,20 +2172,20 @@
       <c r="F21" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>17.1</v>
+      <c r="G21" s="8" t="n">
+        <v>71.8</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>23.5</v>
+        <v>3.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18</v>
@@ -2185,8 +2193,8 @@
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>28</v>
+      <c r="N21" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2194,9 +2202,7 @@
       <c r="P21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>19.9</v>
       </c>
@@ -2204,10 +2210,10 @@
         <v>28.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>22</v>
@@ -2241,13 +2247,13 @@
         <v>339.2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>27.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22.3</v>
+        <v>92.3</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.6</v>
@@ -2259,19 +2265,19 @@
         <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>16.2</v>
+        <v>14.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>21.6</v>
+        <v>2.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2289,7 +2295,7 @@
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14</v>
+        <v>724</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2307,7 +2313,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2322,72 +2328,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1542.6</v>
+      </c>
       <c r="D23" s="3" t="n">
-        <v>7.6</v>
+        <v>137.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>352.6</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>14.2</v>
+        <v>74.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>129</v>
+        <v>119.3</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>60.6</v>
+        <v>6.6</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>907.6</v>
+        <v>0.9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>87.8</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>8115.8</v>
+        <v>215.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>393.1</v>
+        <v>293.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>93.2</v>
+        <v>33.2</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>110.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>28.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>771.3</v>
+        <v>110.9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>606.8</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2407,36 +2413,38 @@
       <c r="D24" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="E24" s="3" t="n">
-        <v>3.8</v>
+      <c r="E24" s="8" t="n">
+        <v>70.09999999999999</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G24" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>14.8</v>
+      <c r="H24" s="8" t="n">
+        <v>184.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>9.4</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>48.1</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>26.2</v>
+        <v>1.6</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>938.1</v>
+        <v>93.8</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.3</v>
@@ -2448,26 +2456,28 @@
         <v>10.1</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>874.6</v>
+        <v>78.7</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>22.6</v>
+        <v>28.1</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>21183.4</v>
-      </c>
-      <c r="Y24" s="3" t="inlineStr"/>
+        <v>8181.1</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="Z24" s="3" t="n">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2483,7 +2493,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>279.8</v>
+        <v>479.9</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>24.7</v>
@@ -2494,33 +2504,37 @@
       <c r="F25" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="n">
+        <v>7.5</v>
+      </c>
       <c r="H25" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="L25" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="N25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O25" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Q25" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>22.1</v>
@@ -2529,22 +2543,22 @@
         <v>82.5</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V25" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="Y25" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="Z25" s="3" t="n">
         <v>18</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>16.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2560,7 +2574,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>371.4</v>
+        <v>341.1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>24.8</v>
@@ -2569,22 +2583,22 @@
         <v>15.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>22.9</v>
+        <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>17</v>
@@ -2593,7 +2607,7 @@
         <v>16.7</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>12.8</v>
+        <v>1.1</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>97</v>
@@ -2601,13 +2615,13 @@
       <c r="P26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q26" s="8" t="n">
-        <v>32.7</v>
+      <c r="Q26" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S26" s="3" t="n">
+      <c r="S26" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="T26" s="3" t="n">
@@ -2623,7 +2637,7 @@
         <v>19.7</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>28.4</v>
+        <v>22.4</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>92</v>
@@ -2651,7 +2665,7 @@
         <v>26.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.6</v>
+        <v>16.7</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>21.7</v>
@@ -2660,7 +2674,7 @@
         <v>10.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>460.5</v>
+        <v>16</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2.5</v>
@@ -2669,15 +2683,17 @@
         <v>3.5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L27" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O27" s="3" t="n">
         <v>93</v>
       </c>
@@ -2691,9 +2707,11 @@
         <v>21.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="T27" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>69.59999999999999</v>
+      </c>
       <c r="U27" s="3" t="n">
         <v>9.9</v>
       </c>
@@ -2703,11 +2721,11 @@
       <c r="W27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>20.8</v>
+      <c r="X27" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>838.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>14</v>
@@ -2726,22 +2744,20 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>453.6</v>
+        <v>45.3</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>25</v>
-      </c>
+      <c r="E28" s="3" t="inlineStr"/>
       <c r="F28" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>3.3</v>
@@ -2750,50 +2766,52 @@
         <v>5.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="M28" s="3" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18</v>
+        <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>840.8</v>
+        <v>840.6</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="Q28" s="8" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="T28" s="3" t="inlineStr"/>
-      <c r="U28" s="8" t="n">
-        <v>62.1</v>
+      <c r="T28" s="3" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>26.8</v>
+      <c r="W28" s="8" t="n">
+        <v>864.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>77.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2809,19 +2827,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2343.6</v>
+        <v>343.6</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>101.4</v>
+        <v>21.4</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>91.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>14</v>
@@ -2830,18 +2848,20 @@
         <v>2.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46.6</v>
+        <v>16.6</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="O29" s="3" t="n">
         <v>86.5</v>
       </c>
@@ -2854,11 +2874,11 @@
       <c r="R29" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>21.5</v>
+        <v>81.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.8</v>
@@ -2869,8 +2889,8 @@
       <c r="W29" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>6.9</v>
+      <c r="X29" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>88</v>
@@ -2892,21 +2912,25 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>78.8</v>
+        <v>178.8</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
+        <v>138.4</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="F30" s="3" t="n">
-        <v>60.9</v>
+        <v>106.4</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="n">
+        <v>710.7</v>
+      </c>
       <c r="I30" s="3" t="n">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>19.3</v>
@@ -2921,39 +2945,43 @@
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>18</v>
+        <v>0.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.4</v>
+        <v>1434.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>8.9</v>
+        <v>58.2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="R30" s="3" t="inlineStr"/>
+        <v>114.2</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>200.2</v>
+      </c>
       <c r="S30" s="3" t="n">
-        <v>2109.4</v>
+        <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>30.3</v>
+        <v>230.3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1681.8</v>
+        <v>111.8</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>91.8</v>
+        <v>191.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
+        <v>998.1</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>416.1</v>
+      </c>
       <c r="Z30" s="3" t="n">
-        <v>0.4</v>
+        <v>20</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2969,74 +2997,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2357.7</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>96.3</v>
+        <v>357.7</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>63.1</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>110</v>
+        <v>16.3</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>26.1</v>
+      <c r="I31" s="8" t="n">
+        <v>96.09999999999999</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.9</v>
+        <v>28.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>372.1</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>21810.1</v>
+        <v>66.2</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>49</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1</v>
+        <v>11.8</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>84.09999999999999</v>
+        <v>1.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>83.2</v>
+        <v>18.1</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>40.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3052,35 +3080,33 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>266.6</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
+        <v>956.6</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>21</v>
+        <v>19.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.4</v>
+        <v>1311.8</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>12.2</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
       <c r="L32" s="3" t="n">
-        <v>19.1</v>
+        <v>4.1</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>15.1</v>
+        <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>8.9</v>
@@ -3088,28 +3114,26 @@
       <c r="O32" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="P32" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>18</v>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="8" t="n">
+        <v>18.3</v>
       </c>
       <c r="R32" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="S32" s="8" t="n">
-        <v>20.4</v>
+      <c r="S32" s="3" t="n">
+        <v>1844151.8</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>98</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W32" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3119,7 +3143,7 @@
         <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>21.1</v>
+        <v>117.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3143,8 +3167,8 @@
       <c r="E33" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>21.7</v>
+      <c r="F33" s="8" t="n">
+        <v>25.1</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.1</v>
@@ -3153,9 +3177,11 @@
         <v>13.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="K33" s="3" t="n">
         <v>5.8</v>
       </c>
@@ -3163,16 +3189,16 @@
         <v>17.1</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.1</v>
+        <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>28.8</v>
+        <v>11.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>7.8</v>
+        <v>78</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>21.4</v>
@@ -3187,9 +3213,9 @@
         <v>77.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="W33" s="8" t="n">
@@ -3199,10 +3225,10 @@
         <v>12.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.8</v>
+        <v>286.5</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>23.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3218,7 +3244,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2350.2</v>
+        <v>350.2</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>24.8</v>
@@ -3230,45 +3256,49 @@
         <v>20.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>7.9</v>
+        <v>17.8</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="L34" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11.9</v>
+        <v>1.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0.7</v>
+        <v>29.3</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="S34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T34" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20.8</v>
@@ -3283,7 +3313,7 @@
         <v>84</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3311,7 +3341,7 @@
         <v>20.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>14.4</v>
@@ -3325,17 +3355,17 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
-        <v>17.6</v>
+      <c r="L35" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.5</v>
+        <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
@@ -3344,16 +3374,16 @@
         <v>22.8</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>21.1</v>
+        <v>19.8</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.1</v>
@@ -3368,7 +3398,7 @@
         <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>21.1</v>
+        <v>12.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3384,7 +3414,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>356.8</v>
+        <v>35.6</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>28.1</v>
@@ -3398,14 +3428,14 @@
       <c r="G36" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>13.7</v>
+      <c r="H36" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4</v>
@@ -3416,9 +3446,11 @@
       <c r="M36" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>13.6</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>4.5</v>
@@ -3433,16 +3465,16 @@
         <v>21.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>60.2</v>
+        <v>168.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>80.8</v>
+        <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>18.8</v>
+        <v>19.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>22.6</v>
@@ -3451,7 +3483,7 @@
         <v>95.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.8</v>
+        <v>41.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3467,16 +3499,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1645.2</v>
+        <v>164.3</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1182.8</v>
+        <v>231.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1609.1</v>
+        <v>107.1</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>48.5</v>
@@ -3485,53 +3517,55 @@
         <v>710.6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>116.7</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>160.6</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
+        <v>88.5</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="N37" s="3" t="n">
-        <v>86.8</v>
+        <v>8.6</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>228</v>
+        <v>899.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>120.8</v>
+        <v>12</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>1812.3</v>
+        <v>222.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>100.8</v>
+        <v>103.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>289.4</v>
+        <v>9383.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>98.09999999999999</v>
-      </c>
+        <v>34.2</v>
+      </c>
+      <c r="V37" s="3" t="inlineStr"/>
       <c r="W37" s="3" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="X37" s="3" t="inlineStr"/>
+        <v>923.1</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="Y37" s="3" t="n">
-        <v>418.8</v>
-      </c>
-      <c r="Z37" s="3" t="inlineStr"/>
+        <v>218.7</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3546,71 +3580,75 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1292.8</v>
+        <v>329.6</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>634.1</v>
+        <v>26.3</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>66.09999999999999</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I38" s="3" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="n">
-        <v>33.1</v>
+        <v>3.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>17.7</v>
+        <v>12.6</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>688.9</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>796.1</v>
+        <v>16.1</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>0.8</v>
+      <c r="Q38" s="8" t="n">
+        <v>225.1</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>11.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="U38" s="3" t="inlineStr"/>
-      <c r="V38" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>20.6</v>
+      <c r="U38" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>0.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>8971.799999999999</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3625,64 +3663,66 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>986.4</v>
+        <v>264.4</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>25.6</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>18.7</v>
+        <v>20.7</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.8</v>
+        <v>33.1</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>3.6</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>22.8</v>
+        <v>29.8</v>
       </c>
       <c r="R39" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
+        <v>23.1</v>
+      </c>
+      <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="n">
-        <v>20</v>
+        <v>18.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3698,74 +3738,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>359</v>
+        <v>286.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>27.5</v>
+        <v>25.6</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>7.9</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>15.8</v>
+        <v>0.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>76.2</v>
+        <v>82.5</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>25.8</v>
+        <v>22.8</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>20.4</v>
+        <v>19.5</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>12.8</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>32.4</v>
+        <v>22.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3781,70 +3823,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>4866.4</v>
+        <v>359</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>28.3</v>
+        <v>51.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17</v>
+        <v>15.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>20.5</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>15.7</v>
+        <v>18</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>55.3</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>16.8</v>
+        <v>11.9</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>22</v>
+        <v>76.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q41" s="8" t="n">
-        <v>26</v>
+        <v>4.8</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>19.5</v>
+        <v>20.2</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>14.1</v>
+        <v>61.4</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="W41" s="3" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="X41" s="3" t="n">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3860,69 +3906,71 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>242.6</v>
+        <v>4856.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>18.9</v>
+        <v>22.8</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>10.1</v>
+        <v>22.9</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>79.8</v>
+        <v>682</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="R42" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X42" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Y42" s="3" t="n">
-        <v>23.4</v>
+        <v>28.5</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>7.1</v>
@@ -3941,71 +3989,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D43" s="8" t="n">
+        <v>742.6</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R43" s="8" t="n">
-        <v>61.6</v>
+      <c r="R43" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="n">
-        <v>20.8</v>
+        <v>55.5</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X43" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z43" s="3" t="inlineStr"/>
+        <v>20.4</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4059,75 +4111,75 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>362.9</v>
+        <v>1889</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>16.4</v>
-      </c>
+        <v>134.4</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="n">
-        <v>21.6</v>
+        <v>108.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.5</v>
+        <v>59.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>13.9</v>
+        <v>69.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.5</v>
+        <v>117.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>18</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>15.9</v>
+        <v>53.7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1.6</v>
+        <v>71</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>1405.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>9.9</v>
+        <v>19.5</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>1268.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>202.8</v>
+        <v>101.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>20.8</v>
+        <v>104.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>66</v>
+        <v>330</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.1</v>
+        <v>55.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21</v>
+        <v>104.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>18.7</v>
+        <v>98.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>20.2</v>
+        <v>118.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>108.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4141,64 +4193,78 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="n">
+        <v>362.9</v>
+      </c>
       <c r="D46" s="3" t="n">
-        <v>0.8</v>
+        <v>26.9</v>
       </c>
       <c r="E46" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>439.8</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.8</v>
-      </c>
       <c r="V46" s="3" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X46" s="3" t="inlineStr"/>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -739,13 +730,13 @@
         <v>389.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>88.3</v>
+        <v>28.3</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12.5</v>
@@ -760,19 +751,19 @@
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2</v>
@@ -790,7 +781,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>20.3</v>
@@ -819,7 +810,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.6</v>
+        <v>32.6</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>98.59999999999999</v>
@@ -830,11 +821,11 @@
       <c r="F5" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>121</v>
+      <c r="G5" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -858,7 +849,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>24.8</v>
@@ -870,10 +861,10 @@
         <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>84.3</v>
+        <v>74.3</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>18</v>
@@ -881,7 +872,7 @@
       <c r="W5" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y5" s="3" t="n">
@@ -904,7 +895,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>494.4</v>
+        <v>484.4</v>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="n">
@@ -916,17 +907,17 @@
       <c r="G6" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>25.2</v>
+      <c r="H6" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>15.7</v>
+        <v>5.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>17.2</v>
@@ -935,7 +926,7 @@
         <v>16.4</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
@@ -961,7 +952,7 @@
       <c r="V6" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -971,7 +962,7 @@
         <v>91</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -987,7 +978,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>384.4</v>
+        <v>374.4</v>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
@@ -1003,7 +994,7 @@
         <v>12.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.8</v>
@@ -1036,7 +1027,7 @@
         <v>24.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>18.7</v>
+        <v>68.7</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>11.4</v>
@@ -1070,7 +1061,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>460.2</v>
+        <v>60.2</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>28.4</v>
@@ -1109,7 +1100,7 @@
         <v>88.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>24.5</v>
@@ -1155,7 +1146,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2240.4</v>
+        <v>140.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>142</v>
@@ -1167,10 +1158,10 @@
         <v>12.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>259.1</v>
+        <v>59.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>671.7</v>
+        <v>67.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.2</v>
@@ -1189,13 +1180,13 @@
       </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>343.3</v>
+        <v>345.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1272.1</v>
+        <v>127.1</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>110.9</v>
@@ -1210,13 +1201,13 @@
         <v>38.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>28.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>92.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>63.8</v>
+        <v>3.1</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>445.1</v>
@@ -1238,13 +1229,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>428.1</v>
+        <v>28.1</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>66.09999999999999</v>
+      <c r="E10" s="3" t="n">
+        <v>166.1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.5</v>
@@ -1252,19 +1243,19 @@
       <c r="G10" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>18.5</v>
+      <c r="H10" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L10" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="M10" s="3" t="n">
@@ -1275,19 +1266,19 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>26.4</v>
+        <v>25.4</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1041.4</v>
+        <v>1011.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>7.7</v>
@@ -1305,7 +1296,7 @@
         <v>89</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>161.4</v>
+        <v>211.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1333,13 +1324,13 @@
         <v>21.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>92.8</v>
+      <c r="I11" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>5.1</v>
@@ -1352,7 +1343,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
@@ -1379,8 +1370,8 @@
       <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X11" s="8" t="n">
-        <v>822</v>
+      <c r="X11" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>84.5</v>
@@ -1428,14 +1419,14 @@
       <c r="K12" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>81.40000000000001</v>
+      <c r="L12" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1446,10 +1437,10 @@
       <c r="Q12" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="R12" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T12" s="3" t="n">
@@ -1498,27 +1489,27 @@
       <c r="F13" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="8" t="n">
-        <v>21</v>
+      <c r="J13" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>92.2</v>
@@ -1536,7 +1527,7 @@
         <v>23.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>27.5</v>
+        <v>77.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.8</v>
@@ -1578,8 +1569,8 @@
       <c r="E14" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>821.1</v>
+      <c r="F14" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>7.4</v>
@@ -1589,7 +1580,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
@@ -1607,7 +1598,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>12.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>21</v>
@@ -1615,7 +1606,7 @@
       <c r="R14" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="T14" s="3" t="n">
@@ -1634,7 +1625,7 @@
         <v>22.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>0.7</v>
@@ -1653,7 +1644,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>334.8</v>
+        <v>834.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>28.3</v>
@@ -1661,8 +1652,8 @@
       <c r="E15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>8.5</v>
+      <c r="F15" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11.7</v>
@@ -1671,13 +1662,13 @@
         <v>14.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>17.2</v>
@@ -1686,7 +1677,7 @@
         <v>16.6</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>94</v>
@@ -1695,19 +1686,19 @@
         <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>59.3</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>16</v>
+      <c r="U15" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>19.2</v>
@@ -1719,10 +1710,10 @@
         <v>20.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1738,7 +1729,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1361.8</v>
+        <v>1561.8</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>134</v>
@@ -1750,19 +1741,19 @@
         <v>109.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>481.4</v>
+        <v>28.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>73</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>110.8</v>
+        <v>10.8</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>88.8</v>
@@ -1771,25 +1762,25 @@
         <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1465.9</v>
+        <v>22.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1089.3</v>
+        <v>119.3</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>104.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>2116.6</v>
+        <v>114.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>199.8</v>
+        <v>393.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>35.1</v>
@@ -1798,13 +1789,13 @@
         <v>101.9</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>969.1</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>98.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>458.4</v>
+        <v>457.4</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1821,16 +1812,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2312.4</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>40.1</v>
+        <v>312.4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>29.7</v>
@@ -1839,19 +1830,19 @@
         <v>14.6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1.9</v>
@@ -1865,29 +1856,29 @@
       <c r="Q17" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="8" t="n">
-        <v>189.1</v>
+      <c r="R17" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>29.9</v>
+        <v>22.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>789.1</v>
+        <v>78.8</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>211.6</v>
+      <c r="V17" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>2812.1</v>
+        <v>288.1</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2.1</v>
@@ -1914,13 +1905,13 @@
       <c r="E18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>90.90000000000001</v>
+      <c r="F18" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
@@ -1930,7 +1921,7 @@
         <v>5.5</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>18.2</v>
@@ -1939,13 +1930,13 @@
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>9.6</v>
@@ -1954,25 +1945,25 @@
         <v>21.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>166.5</v>
+        <v>66.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>14.7</v>
+        <v>11.7</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>22488.4</v>
+        <v>22421.4</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>111.1</v>
+        <v>281.2</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>118.9</v>
+        <v>18.9</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>20.7</v>
@@ -1991,7 +1982,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>219.4</v>
+        <v>19.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>27.4</v>
@@ -2009,22 +2000,22 @@
         <v>14.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>22.8</v>
+        <v>2.2</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>1.8</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
@@ -2036,16 +2027,16 @@
         <v>23.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>8.6</v>
+        <v>20.2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>13.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>23.4</v>
@@ -2057,7 +2048,7 @@
         <v>21.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>19.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>7.6</v>
@@ -2078,7 +2069,7 @@
       <c r="C20" s="3" t="n">
         <v>358.8</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -2097,7 +2088,7 @@
         <v>19.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>53.1</v>
+        <v>23.1</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -2109,13 +2100,13 @@
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>22.8</v>
@@ -2123,11 +2114,11 @@
       <c r="R20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>1891.8</v>
+        <v>89</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
@@ -2161,7 +2152,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2284.2</v>
+        <v>284.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>68.09999999999999</v>
@@ -2172,14 +2163,14 @@
       <c r="F21" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <v>71.8</v>
+      <c r="G21" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>8</v>
+        <v>20.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.2</v>
@@ -2194,26 +2185,26 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>22</v>
@@ -2247,13 +2238,13 @@
         <v>339.2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>92.3</v>
+        <v>22.3</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.6</v>
@@ -2265,7 +2256,7 @@
         <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2277,7 +2268,7 @@
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2295,7 +2286,7 @@
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>724</v>
+        <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2329,7 +2320,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1542.6</v>
+        <v>1548.6</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>137.6</v>
@@ -2338,19 +2329,19 @@
         <v>85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>18.1</v>
+        <v>11.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>352.6</v>
+        <v>52.6</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>74.8</v>
+        <v>74.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>119.3</v>
+        <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.6</v>
@@ -2359,10 +2350,10 @@
         <v>0.9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
@@ -2371,10 +2362,10 @@
       <c r="Q23" s="3" t="inlineStr"/>
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>215.8</v>
+        <v>115.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>293.1</v>
+        <v>93.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>33.2</v>
@@ -2386,13 +2377,13 @@
         <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>110.9</v>
+        <v>103.4</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>606.8</v>
+        <v>16.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2413,26 +2404,26 @@
       <c r="D24" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="E24" s="8" t="n">
-        <v>70.09999999999999</v>
+      <c r="E24" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>29.2</v>
+        <v>22.2</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>184.8</v>
+      <c r="H24" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>48.1</v>
@@ -2441,7 +2432,7 @@
         <v>17.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>93.8</v>
@@ -2449,14 +2440,14 @@
       <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>10.1</v>
+      <c r="Q24" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>78.7</v>
@@ -2470,14 +2461,14 @@
       <c r="W24" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="X24" s="8" t="n">
-        <v>8181.1</v>
+      <c r="X24" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2505,20 +2496,20 @@
         <v>21.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2543,16 +2534,16 @@
         <v>82.5</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="W25" s="8" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="X25" s="8" t="n">
-        <v>54.4</v>
+        <v>4.7</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>55.5</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>21.1</v>
@@ -2574,7 +2565,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>341.1</v>
+        <v>341.4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>24.8</v>
@@ -2586,16 +2577,16 @@
         <v>20.3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>2.6</v>
@@ -2621,16 +2612,16 @@
       <c r="R26" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S26" s="8" t="n">
+      <c r="S26" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V26" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2698,13 +2689,13 @@
         <v>93</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>22.7</v>
@@ -2721,14 +2712,14 @@
       <c r="W27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X27" s="8" t="n">
+      <c r="X27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2744,7 +2735,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>45.3</v>
+        <v>453.6</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>28.8</v>
@@ -2756,7 +2747,7 @@
       <c r="G28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2771,14 +2762,14 @@
       <c r="L28" s="3" t="n">
         <v>46.1</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>840.6</v>
+        <v>24</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.1</v>
@@ -2787,7 +2778,7 @@
         <v>20.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>18.4</v>
@@ -2801,11 +2792,11 @@
       <c r="V28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W28" s="8" t="n">
-        <v>864.1</v>
+      <c r="W28" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>77.5</v>
@@ -2833,7 +2824,7 @@
         <v>26.3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>21.4</v>
@@ -2860,7 +2851,7 @@
         <v>15.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>86.5</v>
@@ -2872,9 +2863,9 @@
         <v>22</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S29" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2884,7 +2875,7 @@
         <v>4.8</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>18.8</v>
@@ -2912,13 +2903,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>178.8</v>
+        <v>1788.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>138.4</v>
+        <v>131.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>14.1</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>106.4</v>
@@ -2927,10 +2918,10 @@
         <v>50</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>710.7</v>
+        <v>70.7</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>19.3</v>
@@ -2945,40 +2936,40 @@
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1434.5</v>
+        <v>454.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>58.2</v>
+        <v>28.9</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>114.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>200.2</v>
+        <v>100.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>322.2</v>
+        <v>92.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>230.3</v>
+        <v>30.3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>111.8</v>
+        <v>101.8</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>998.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>416.1</v>
+        <v>16.1</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>20</v>
@@ -2999,8 +2990,8 @@
       <c r="C31" s="3" t="n">
         <v>357.7</v>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>63.1</v>
+      <c r="D31" s="3" t="n">
+        <v>263.1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>16.3</v>
@@ -3009,62 +3000,62 @@
         <v>21.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I31" s="8" t="n">
-        <v>96.09999999999999</v>
+      <c r="I31" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>28.9</v>
+        <v>8.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>372.1</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>66.2</v>
+        <v>1.4</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V31" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="X31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>11.1</v>
-      </c>
       <c r="Y31" s="3" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3085,20 +3076,20 @@
       <c r="D32" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1311.8</v>
+        <v>131.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr"/>
@@ -3109,23 +3100,23 @@
         <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="8" t="n">
+      <c r="Q32" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1844151.8</v>
+        <v>158.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0.7</v>
@@ -3133,7 +3124,7 @@
       <c r="V32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3143,7 +3134,7 @@
         <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>117.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3167,8 +3158,8 @@
       <c r="E33" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>25.1</v>
+      <c r="F33" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.1</v>
@@ -3180,7 +3171,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>18.9</v>
+        <v>3.9</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>5.8</v>
@@ -3192,7 +3183,7 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>11.4</v>
+        <v>1.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>78</v>
@@ -3213,22 +3204,22 @@
         <v>77.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>28</v>
+      <c r="W33" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>12.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>286.5</v>
+        <v>86</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3256,24 +3247,24 @@
         <v>20.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H34" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3283,16 +3274,16 @@
         <v>91</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>74.8</v>
@@ -3301,7 +3292,7 @@
         <v>7.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>18.8</v>
@@ -3355,8 +3346,8 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
-        <v>88.59999999999999</v>
+      <c r="L35" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.4</v>
@@ -3365,7 +3356,7 @@
         <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
@@ -3374,13 +3365,13 @@
         <v>22.8</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S35" s="8" t="n">
-        <v>28.1</v>
+        <v>19.7</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>6.7</v>
@@ -3398,7 +3389,7 @@
         <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3414,7 +3405,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>35.6</v>
+        <v>356.8</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>28.1</v>
@@ -3428,7 +3419,7 @@
       <c r="G36" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3447,10 +3438,10 @@
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>13.6</v>
+        <v>13.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>4.5</v>
@@ -3465,16 +3456,16 @@
         <v>21.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>168.2</v>
+        <v>60.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>20.8</v>
+      <c r="V36" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>22.6</v>
@@ -3483,7 +3474,7 @@
         <v>95.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>41.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3499,10 +3490,10 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>164.3</v>
+        <v>643.2</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>231.4</v>
+        <v>131.4</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>82.90000000000001</v>
@@ -3514,7 +3505,7 @@
         <v>48.5</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>710.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>10.5</v>
@@ -3524,47 +3515,47 @@
         <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>17.8</v>
+        <v>77</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>899.8</v>
+        <v>39.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>222.9</v>
+        <v>112.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>103.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>9383.4</v>
+        <v>385.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>34.2</v>
+        <v>24.2</v>
       </c>
       <c r="V37" s="3" t="inlineStr"/>
       <c r="W37" s="3" t="n">
-        <v>923.1</v>
+        <v>23.1</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>218.7</v>
+        <v>48.7</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3580,16 +3571,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>329.6</v>
+        <v>28.6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E38" s="8" t="n">
-        <v>66.09999999999999</v>
+      <c r="E38" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.699999999999999</v>
@@ -3602,52 +3593,52 @@
         <v>3.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>688.9</v>
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>16.1</v>
+        <v>10.1</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
-        <v>225.1</v>
+      <c r="Q38" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>97.09999999999999</v>
+      <c r="S38" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>8971.799999999999</v>
+        <v>89.7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3690,24 +3681,24 @@
       <c r="L39" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>17.8</v>
+      <c r="M39" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>11.8</v>
+        <v>16.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>85</v>
       </c>
       <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>22.2</v>
+        <v>23.7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="3" t="inlineStr"/>
@@ -3718,7 +3709,7 @@
         <v>16.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>88.90000000000001</v>
@@ -3764,14 +3755,14 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
-        <v>7.9</v>
+      <c r="L40" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>82.5</v>
@@ -3785,14 +3776,14 @@
       <c r="R40" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="S40" s="8" t="n">
+      <c r="S40" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20</v>
@@ -3807,7 +3798,7 @@
         <v>89.7</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3832,17 +3823,17 @@
         <v>15.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H41" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.2</v>
@@ -3850,11 +3841,11 @@
       <c r="L41" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>55.3</v>
+      <c r="M41" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>11.9</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>76.2</v>
@@ -3868,14 +3859,14 @@
       <c r="R41" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>9.4</v>
+      <c r="S41" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="U41" s="8" t="n">
-        <v>18.8</v>
+      <c r="U41" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>4.4</v>
@@ -3890,7 +3881,7 @@
         <v>86.2</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3915,10 +3906,10 @@
         <v>17</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>22.9</v>
+        <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>14.1</v>
@@ -3937,10 +3928,10 @@
         <v>15.7</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>682</v>
+        <v>62</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>13.6</v>
@@ -3952,7 +3943,7 @@
         <v>19.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>57.9</v>
@@ -3970,7 +3961,7 @@
         <v>20.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>28.5</v>
+        <v>70.5</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>7.1</v>
@@ -3989,7 +3980,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>742.6</v>
+        <v>28.8</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>27.6</v>
@@ -4000,21 +3991,21 @@
       <c r="F43" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <v>88.5</v>
+      <c r="G43" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>88</v>
+      <c r="L43" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>15.7</v>
@@ -4026,21 +4017,21 @@
         <v>79.8</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>1.9</v>
+        <v>19.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>55.5</v>
       </c>
-      <c r="U43" s="8" t="n">
+      <c r="U43" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="V43" s="3" t="n">
@@ -4049,11 +4040,11 @@
       <c r="W43" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>18.5</v>
+      <c r="X43" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>20.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>7.1</v>
@@ -4111,7 +4102,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1889</v>
+        <v>839</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>134.4</v>
@@ -4121,43 +4112,43 @@
         <v>108.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>59.5</v>
+        <v>52.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>69.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>117.4</v>
+        <v>17.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>53.7</v>
+        <v>25.7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>71</v>
+        <v>21.6</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>1405.5</v>
+        <v>405.5</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1268.4</v>
+        <v>125.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>101.8</v>
+        <v>101</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>104.8</v>
+        <v>104.2</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>330</v>
@@ -4169,16 +4160,16 @@
         <v>104.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>98.5</v>
+        <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>118.2</v>
+        <v>1.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>108.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11.4</v>
+        <v>21.1</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4194,7 +4185,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>362.9</v>
+        <v>367.9</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>26.9</v>
@@ -4203,28 +4194,28 @@
         <v>16.4</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>11.8</v>
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>439.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>11.1</v>
+        <v>1.5</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>65.90000000000001</v>
+      <c r="M46" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>1.6</v>
@@ -4233,37 +4224,37 @@
         <v>81.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>11.1</v>
+        <v>1.5</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>12.4</v>
+        <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z46" s="3" t="n">
         <v>11.4</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>11.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -760,7 +760,7 @@
         <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>90</v>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>32.6</v>
+        <v>431.6</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>98.59999999999999</v>
@@ -825,7 +825,7 @@
         <v>11.3</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -926,7 +926,7 @@
         <v>16.4</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
@@ -1012,7 +1012,7 @@
         <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89.8</v>
+        <v>22.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>60.2</v>
+        <v>460.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>28.4</v>
+        <v>22.4</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>17</v>
@@ -1100,7 +1100,7 @@
         <v>88.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>24.5</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>140.4</v>
+        <v>2140.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>142</v>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28.1</v>
+        <v>428.1</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>166.1</v>
+        <v>16.6</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.5</v>
@@ -1266,7 +1266,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>25.4</v>
@@ -1275,7 +1275,7 @@
         <v>1.1</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1011.4</v>
+        <v>1214.1</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>76.8</v>
@@ -1296,7 +1296,7 @@
         <v>89</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>211.4</v>
+        <v>1811.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
@@ -1426,7 +1426,7 @@
         <v>17.6</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1509,7 +1509,7 @@
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>92.2</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>21.2</v>
+        <v>121.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
@@ -1592,7 +1592,7 @@
         <v>17.2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>834.8</v>
+        <v>334.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>28.3</v>
@@ -1677,7 +1677,7 @@
         <v>16.6</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>94</v>
@@ -1698,7 +1698,7 @@
         <v>59.3</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>19.2</v>
@@ -1741,7 +1741,7 @@
         <v>109.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>28.4</v>
+        <v>48.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>73</v>
@@ -1762,10 +1762,10 @@
         <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>22.8</v>
+        <v>465.9</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
@@ -1857,13 +1857,13 @@
         <v>23.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>22.9</v>
+        <v>26.9</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.8</v>
+        <v>788.1</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
@@ -1878,7 +1878,7 @@
         <v>21.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>288.1</v>
+        <v>202.2</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2.1</v>
@@ -1930,7 +1930,7 @@
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87.09999999999999</v>
@@ -1954,10 +1954,10 @@
         <v>11.7</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>22421.4</v>
+        <v>22621.4</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>281.2</v>
+        <v>1421.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>20.9</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>19.4</v>
+        <v>319.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>27.4</v>
@@ -2015,7 +2015,7 @@
         <v>17.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
@@ -2088,7 +2088,7 @@
         <v>19.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>23.1</v>
+        <v>3.1</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -2118,7 +2118,7 @@
         <v>24.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>89</v>
+        <v>28.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
@@ -2167,7 +2167,7 @@
         <v>11.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>20.2</v>
+        <v>14</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.5</v>
@@ -2185,7 +2185,7 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2268,7 +2268,7 @@
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2329,7 +2329,7 @@
         <v>85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11.2</v>
+        <v>111.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>52.6</v>
@@ -2353,7 +2353,7 @@
         <v>87.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
@@ -2365,7 +2365,7 @@
         <v>115.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>93.7</v>
+        <v>393.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>33.2</v>
@@ -2377,7 +2377,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>103.4</v>
+        <v>1103.4</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>16.8</v>
@@ -2456,13 +2456,13 @@
         <v>6.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>2.1</v>
+        <v>228.1</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>83.40000000000001</v>
@@ -2513,7 +2513,7 @@
         <v>18.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>9.4</v>
@@ -2537,13 +2537,13 @@
         <v>4.7</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>5.8</v>
+        <v>211.4</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>0.5</v>
+        <v>21.4</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>55.5</v>
+        <v>262.4</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>21.1</v>
@@ -2592,7 +2592,7 @@
         <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>17</v>
+        <v>28.2</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>16.7</v>
@@ -2619,7 +2619,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>20.6</v>
@@ -2781,7 +2781,7 @@
         <v>17.7</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>18.4</v>
+        <v>28.2</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>74.7</v>
@@ -2851,7 +2851,7 @@
         <v>15.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.4</v>
+        <v>18.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>86.5</v>
@@ -2909,7 +2909,7 @@
         <v>131.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14.1</v>
+        <v>814.1</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>106.4</v>
@@ -2930,13 +2930,13 @@
         <v>7.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>454.5</v>
@@ -2954,13 +2954,13 @@
         <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>92.2</v>
+        <v>392.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>101.8</v>
+        <v>161.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>91.8</v>
@@ -2969,7 +2969,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>16.1</v>
+        <v>116.1</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>20</v>
@@ -2991,7 +2991,7 @@
         <v>357.7</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>263.1</v>
+        <v>26.4</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>16.3</v>
@@ -3006,13 +3006,13 @@
         <v>14.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.6</v>
+        <v>26.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>8.9</v>
+        <v>3.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>172.1</v>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1.8</v>
@@ -3046,10 +3046,10 @@
         <v>25.1</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.1</v>
+        <v>21.1</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>18.4</v>
@@ -3086,7 +3086,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>131.5</v>
+        <v>130.1</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.2</v>
@@ -3100,7 +3100,7 @@
         <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>72</v>
@@ -3113,7 +3113,7 @@
         <v>18</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>158.8</v>
+        <v>2611.4</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>97</v>
@@ -3259,7 +3259,7 @@
         <v>3.7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.5</v>
@@ -3268,7 +3268,7 @@
         <v>16.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>91</v>
@@ -3347,16 +3347,16 @@
         <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>18.6</v>
+        <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
@@ -3438,7 +3438,7 @@
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>13.1</v>
+        <v>19.1</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>77</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>643.2</v>
+        <v>1643.2</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>131.4</v>
@@ -3524,7 +3524,7 @@
         <v>8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>39.8</v>
+        <v>839.8</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>2</v>
@@ -3542,17 +3542,17 @@
         <v>385.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.2</v>
+        <v>34.2</v>
       </c>
       <c r="V37" s="3" t="inlineStr"/>
       <c r="W37" s="3" t="n">
-        <v>23.1</v>
+        <v>923.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>48.7</v>
+        <v>148.7</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>1.1</v>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>28.6</v>
+        <v>328.6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>26.3</v>
@@ -3605,7 +3605,7 @@
         <v>1.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
@@ -3617,7 +3617,7 @@
         <v>19.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>20.8</v>
+        <v>208.1</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>77.09999999999999</v>
@@ -3626,19 +3626,19 @@
         <v>6.8</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>196.1</v>
+        <v>19.6</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>185.1</v>
+        <v>18.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>89.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>17.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>85</v>
@@ -3695,7 +3695,7 @@
         <v>23.7</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>21.2</v>
+        <v>22.2</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>23.7</v>
@@ -3738,7 +3738,7 @@
         <v>15.8</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>9.800000000000001</v>
@@ -3762,7 +3762,7 @@
         <v>15.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>82.5</v>
@@ -3845,7 +3845,7 @@
         <v>15.3</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>76.2</v>
@@ -3928,13 +3928,13 @@
         <v>15.7</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16</v>
+        <v>2.6</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>62</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>26</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>28.8</v>
+        <v>442.6</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>27.6</v>
@@ -4011,7 +4011,7 @@
         <v>15.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>79.8</v>
@@ -4044,7 +4044,7 @@
         <v>19.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>2.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>7.1</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>839</v>
+        <v>1839</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>134.4</v>
@@ -4130,10 +4130,10 @@
         <v>90.2</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>25.7</v>
+        <v>23.7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>21.6</v>
+        <v>11.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>405.5</v>
@@ -4163,13 +4163,13 @@
         <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>21.6</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>439.8</v>
@@ -4209,7 +4209,7 @@
         <v>5.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18</v>
@@ -4230,31 +4230,31 @@
         <v>25.1</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>80</v>
+        <v>20.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>1.5</v>
+        <v>11.4</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>11.4</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -760,7 +760,7 @@
         <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>90</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>374.4</v>
+        <v>37.4</v>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
@@ -1012,7 +1012,7 @@
         <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.8</v>
+        <v>89.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1064,7 +1064,7 @@
         <v>460.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>22.4</v>
+        <v>28.4</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>17</v>
@@ -1094,13 +1094,13 @@
         <v>15.8</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>24.5</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2140.4</v>
+        <v>214</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>142</v>
@@ -1155,7 +1155,7 @@
         <v>829.1</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>12.4</v>
+        <v>112.4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>59.1</v>
@@ -1207,7 +1207,7 @@
         <v>92.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>3.1</v>
+        <v>103.1</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>445.1</v>
@@ -1266,16 +1266,16 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1214.1</v>
+        <v>42</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>76.8</v>
@@ -1296,7 +1296,7 @@
         <v>89</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1811.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
@@ -1426,7 +1426,7 @@
         <v>17.6</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>92.09999999999999</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>92.2</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>121.2</v>
+        <v>21.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
@@ -1592,7 +1592,7 @@
         <v>17.2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
@@ -1677,7 +1677,7 @@
         <v>16.6</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>94</v>
@@ -1762,7 +1762,7 @@
         <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>465.9</v>
@@ -1824,7 +1824,7 @@
         <v>22</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>29.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
@@ -1836,7 +1836,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>17.8</v>
@@ -1863,7 +1863,7 @@
         <v>22.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>788.1</v>
+        <v>78.8</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
@@ -1878,7 +1878,7 @@
         <v>21.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>202.2</v>
+        <v>200.1</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2.1</v>
@@ -1930,7 +1930,7 @@
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87.09999999999999</v>
@@ -1954,10 +1954,10 @@
         <v>11.7</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>22621.4</v>
+        <v>8000</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>1421.4</v>
+        <v>182</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>20.9</v>
@@ -2100,7 +2100,7 @@
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2118,7 +2118,7 @@
         <v>24.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>28.2</v>
+        <v>89</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
@@ -2164,10 +2164,10 @@
         <v>22.5</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.5</v>
@@ -2185,7 +2185,7 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2268,7 +2268,7 @@
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2329,7 +2329,7 @@
         <v>85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>111.2</v>
+        <v>101.8</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>52.6</v>
@@ -2353,7 +2353,7 @@
         <v>87.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
@@ -2377,10 +2377,10 @@
         <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>1103.4</v>
+        <v>110.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>16.8</v>
+        <v>116.8</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>22.7</v>
@@ -2423,7 +2423,7 @@
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>48.1</v>
@@ -2462,7 +2462,7 @@
         <v>19.9</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>228.1</v>
+        <v>22.8</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>83.40000000000001</v>
@@ -2537,13 +2537,13 @@
         <v>4.7</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>211.4</v>
+        <v>2</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>21.4</v>
+        <v>0.2</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>262.4</v>
+        <v>20</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>21.1</v>
@@ -2592,7 +2592,7 @@
         <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>28.2</v>
+        <v>17</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>16.7</v>
@@ -2769,7 +2769,7 @@
         <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.1</v>
@@ -2781,7 +2781,7 @@
         <v>17.7</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>28.2</v>
+        <v>18.4</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>74.7</v>
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1788.4</v>
+        <v>178.8</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>131.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>814.1</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>106.4</v>
@@ -2930,7 +2930,7 @@
         <v>7.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>28.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>81.2</v>
@@ -2942,7 +2942,7 @@
         <v>454.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>28.9</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>114.2</v>
@@ -2954,13 +2954,13 @@
         <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>392.2</v>
+        <v>39.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>161.8</v>
+        <v>101.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>91.8</v>
@@ -2969,7 +2969,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>116.1</v>
+        <v>20.8</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>20</v>
@@ -2991,7 +2991,7 @@
         <v>357.7</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>16.3</v>
@@ -3006,16 +3006,16 @@
         <v>14.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>26.1</v>
+        <v>2.6</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>172.1</v>
+        <v>17.2</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.2</v>
@@ -3043,13 +3043,13 @@
         <v>6.1</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>25.1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>18.4</v>
@@ -3086,7 +3086,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>130.1</v>
+        <v>130</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.2</v>
@@ -3100,7 +3100,7 @@
         <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>72</v>
@@ -3113,7 +3113,7 @@
         <v>18</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>2611.4</v>
+        <v>0.2</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>97</v>
@@ -3183,7 +3183,7 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>78</v>
@@ -3268,7 +3268,7 @@
         <v>16.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>91</v>
@@ -3353,7 +3353,7 @@
         <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>80</v>
@@ -3438,7 +3438,7 @@
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>19.1</v>
+        <v>1.4</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>77</v>
@@ -3462,10 +3462,10 @@
         <v>13.9</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>19.7</v>
+        <v>18.7</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>22.6</v>
@@ -3474,7 +3474,7 @@
         <v>95.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3546,16 +3546,16 @@
       </c>
       <c r="V37" s="3" t="inlineStr"/>
       <c r="W37" s="3" t="n">
-        <v>923.1</v>
+        <v>92.3</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>148.7</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>1.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
@@ -3617,7 +3617,7 @@
         <v>19.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>208.1</v>
+        <v>20.8</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>77.09999999999999</v>
@@ -3685,7 +3685,7 @@
         <v>17.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>85</v>
@@ -3738,7 +3738,7 @@
         <v>15.8</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>26.7</v>
+        <v>20.7</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>9.800000000000001</v>
@@ -3845,7 +3845,7 @@
         <v>15.3</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>76.2</v>
@@ -3928,10 +3928,10 @@
         <v>15.7</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>3.6</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>442.6</v>
+        <v>942.6</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>27.6</v>
@@ -4011,7 +4011,7 @@
         <v>15.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>79.8</v>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1839</v>
+        <v>189</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>134.4</v>
@@ -4133,7 +4133,7 @@
         <v>23.7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>11.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>405.5</v>
@@ -4145,10 +4145,10 @@
         <v>125.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>101</v>
+        <v>101.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>104.2</v>
+        <v>104.8</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>330</v>
@@ -4163,13 +4163,13 @@
         <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>108.7</v>
+        <v>1088.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>21.4</v>
+        <v>1.1</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>21.6</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>439.8</v>
@@ -4209,7 +4209,7 @@
         <v>5.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18</v>
@@ -4233,28 +4233,28 @@
         <v>20.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>11.4</v>
+        <v>1</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
